--- a/p6_deployment/data/germany/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/p6_deployment/data/germany/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,739 +558,1663 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>r7QOmnxn</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>25.72222222222222</v>
-      </c>
-      <c r="D2" t="n">
-        <v>184.8148148148149</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2.066666666666666</v>
-      </c>
-      <c r="F2" t="n">
-        <v>81.1111111111111</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30785185.18518518</v>
-      </c>
-      <c r="H2" t="n">
-        <v>83.87777777777778</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>25.63703703703703</v>
+        <v>25.93146853146853</v>
       </c>
       <c r="J2" t="n">
-        <v>186.037037037037</v>
+        <v>184.7412587412588</v>
       </c>
       <c r="K2" t="n">
-        <v>1.451851851851852</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>74.57777777777778</v>
+        <v>70.13846153846154</v>
       </c>
       <c r="M2" t="n">
-        <v>6745185.185185186</v>
+        <v>2324195.804195804</v>
       </c>
       <c r="N2" t="n">
-        <v>77.25185185185185</v>
-      </c>
-      <c r="O2" t="n">
-        <v>21.98214285714286</v>
-      </c>
-      <c r="P2" t="n">
-        <v>182.5952380952381</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.547619047619048</v>
-      </c>
-      <c r="R2" t="n">
-        <v>76.89285714285715</v>
-      </c>
-      <c r="S2" t="n">
-        <v>31475000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>84.25</v>
-      </c>
+        <v>73.05314685314686</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>23.83333333333333</v>
+        <v>26.21577501445923</v>
       </c>
       <c r="V2" t="n">
-        <v>184.1666666666667</v>
+        <v>185.8954742625795</v>
       </c>
       <c r="W2" t="n">
-        <v>1.208333333333333</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>70.58333333333333</v>
+        <v>66.83335743204164</v>
       </c>
       <c r="Y2" t="n">
-        <v>3646875</v>
+        <v>1262396.616541354</v>
       </c>
       <c r="Z2" t="n">
-        <v>76.29166666666667</v>
+        <v>71.09064488143436</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fBoFTriU</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.03030303030303</v>
+        <v>26.05194805194805</v>
       </c>
       <c r="D3" t="n">
-        <v>184.9393939393939</v>
+        <v>185.6753246753247</v>
       </c>
       <c r="E3" t="n">
-        <v>2.212121212121212</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>79.33333333333333</v>
+        <v>67.1103896103896</v>
       </c>
       <c r="G3" t="n">
-        <v>28430303.03030303</v>
+        <v>1187987.012987013</v>
       </c>
       <c r="H3" t="n">
-        <v>83.06060606060606</v>
+        <v>69.59740259740259</v>
       </c>
       <c r="I3" t="n">
-        <v>25.56969696969697</v>
+        <v>25.90151515151515</v>
       </c>
       <c r="J3" t="n">
-        <v>187.1</v>
+        <v>183.1590909090909</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>1.598484848484848</v>
       </c>
       <c r="L3" t="n">
-        <v>70.58787878787881</v>
+        <v>74.45454545454545</v>
       </c>
       <c r="M3" t="n">
-        <v>2434318.181818182</v>
+        <v>6766666.666666667</v>
       </c>
       <c r="N3" t="n">
-        <v>74.16666666666667</v>
+        <v>78.35606060606061</v>
       </c>
       <c r="O3" t="n">
-        <v>25.14814814814815</v>
+        <v>24.59821428571428</v>
       </c>
       <c r="P3" t="n">
-        <v>183.9259259259259</v>
+        <v>184.0823412698413</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>76.74074074074075</v>
+        <v>64.85813492063491</v>
       </c>
       <c r="S3" t="n">
-        <v>18696296.2962963</v>
+        <v>977405.753968254</v>
       </c>
       <c r="T3" t="n">
-        <v>81.55555555555556</v>
+        <v>68.78769841269842</v>
       </c>
       <c r="U3" t="n">
-        <v>25.59722222222222</v>
+        <v>25.84755291005291</v>
       </c>
       <c r="V3" t="n">
-        <v>186.3564814814815</v>
+        <v>184.9790013227513</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>1.465608465608466</v>
       </c>
       <c r="X3" t="n">
-        <v>68.08333333333333</v>
+        <v>71.76984126984127</v>
       </c>
       <c r="Y3" t="n">
-        <v>1538310.185185185</v>
+        <v>4261069.775132275</v>
       </c>
       <c r="Z3" t="n">
-        <v>71.2175925925926</v>
+        <v>76.27976190476191</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QVFTn6ih</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="n">
-        <v>24.55555555555556</v>
-      </c>
-      <c r="D4" t="n">
-        <v>183.2222222222223</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.703703703703704</v>
-      </c>
-      <c r="F4" t="n">
-        <v>77.55555555555556</v>
-      </c>
-      <c r="G4" t="n">
-        <v>16551851.85185185</v>
-      </c>
-      <c r="H4" t="n">
-        <v>81.18518518518518</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>24.6</v>
+        <v>26.5530303030303</v>
       </c>
       <c r="J4" t="n">
-        <v>182.5333333333333</v>
+        <v>185.8787878787879</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1</v>
+        <v>1.795454545454545</v>
       </c>
       <c r="L4" t="n">
-        <v>80.40000000000001</v>
+        <v>75.31060606060606</v>
       </c>
       <c r="M4" t="n">
-        <v>29816666.66666667</v>
+        <v>8715151.515151516</v>
       </c>
       <c r="N4" t="n">
-        <v>84.03333333333335</v>
-      </c>
-      <c r="O4" t="n">
-        <v>24.875</v>
-      </c>
-      <c r="P4" t="n">
-        <v>183.75</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.416666666666667</v>
-      </c>
-      <c r="R4" t="n">
-        <v>71.33333333333333</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4554166.666666667</v>
-      </c>
-      <c r="T4" t="n">
-        <v>77.41666666666667</v>
-      </c>
+        <v>78.81818181818183</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>25.77777777777778</v>
+        <v>24.07903439153439</v>
       </c>
       <c r="V4" t="n">
-        <v>185.925925925926</v>
+        <v>185.0983796296296</v>
       </c>
       <c r="W4" t="n">
-        <v>1.703703703703704</v>
+        <v>1.308531746031746</v>
       </c>
       <c r="X4" t="n">
-        <v>76.51851851851852</v>
+        <v>70.4890873015873</v>
       </c>
       <c r="Y4" t="n">
-        <v>15377777.77777778</v>
+        <v>4545899.470899471</v>
       </c>
       <c r="Z4" t="n">
-        <v>80.5925925925926</v>
+        <v>77.3587962962963</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8EBlrr6N</t>
+          <t>lONsG15D</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="n">
-        <v>25.66666666666666</v>
-      </c>
-      <c r="D5" t="n">
-        <v>186.6363636363636</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>72.90909090909091</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4484090.909090909</v>
-      </c>
-      <c r="H5" t="n">
-        <v>75.33333333333333</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>24</v>
+        <v>27.18181818181818</v>
       </c>
       <c r="J5" t="n">
-        <v>185.1212121212121</v>
+        <v>185.0419580419581</v>
       </c>
       <c r="K5" t="n">
-        <v>1.363636363636364</v>
+        <v>3.146853146853147</v>
       </c>
       <c r="L5" t="n">
-        <v>72.48484848484848</v>
+        <v>82.37762237762239</v>
       </c>
       <c r="M5" t="n">
-        <v>6006060.606060606</v>
+        <v>44731993.00699301</v>
       </c>
       <c r="N5" t="n">
-        <v>78.27272727272727</v>
-      </c>
-      <c r="O5" t="n">
-        <v>27.51851851851852</v>
-      </c>
-      <c r="P5" t="n">
-        <v>182.6296296296296</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>67.62962962962962</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1204629.62962963</v>
-      </c>
-      <c r="T5" t="n">
-        <v>69.55555555555556</v>
-      </c>
+        <v>84.96503496503496</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>26.2962962962963</v>
+        <v>24.63843101343101</v>
       </c>
       <c r="V5" t="n">
-        <v>184.4444444444444</v>
+        <v>182.2466422466422</v>
       </c>
       <c r="W5" t="n">
-        <v>1.296296296296296</v>
+        <v>2.005494505494505</v>
       </c>
       <c r="X5" t="n">
-        <v>69.25925925925925</v>
+        <v>77.13530219780219</v>
       </c>
       <c r="Y5" t="n">
-        <v>2702592.592592593</v>
+        <v>23187456.12026862</v>
       </c>
       <c r="Z5" t="n">
-        <v>74.7037037037037</v>
+        <v>82.6941391941392</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YeJyopM4</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
-        <v>26.63636363636364</v>
-      </c>
-      <c r="D6" t="n">
-        <v>185.1212121212121</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.787878787878788</v>
-      </c>
-      <c r="F6" t="n">
-        <v>75.09090909090908</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8639393.939393939</v>
-      </c>
-      <c r="H6" t="n">
-        <v>78.75757575757576</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>27.93939393939394</v>
+        <v>24.97855477855478</v>
       </c>
       <c r="J6" t="n">
-        <v>185.4242424242424</v>
+        <v>184.7278943278943</v>
       </c>
       <c r="K6" t="n">
-        <v>3.060606060606061</v>
+        <v>1.500621600621601</v>
       </c>
       <c r="L6" t="n">
-        <v>81.93939393939394</v>
+        <v>75.24040404040404</v>
       </c>
       <c r="M6" t="n">
-        <v>36981818.18181818</v>
+        <v>8566565.656565655</v>
       </c>
       <c r="N6" t="n">
-        <v>84.24242424242424</v>
-      </c>
-      <c r="O6" t="n">
-        <v>24.03703703703704</v>
-      </c>
-      <c r="P6" t="n">
-        <v>186.2592592592593</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="R6" t="n">
-        <v>70.5925925925926</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4445370.37037037</v>
-      </c>
-      <c r="T6" t="n">
-        <v>77.29629629629629</v>
-      </c>
+        <v>78.22665112665113</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>24.59788359788359</v>
+        <v>23.23699633699633</v>
       </c>
       <c r="V6" t="n">
-        <v>182.0291005291006</v>
+        <v>183.7899267399267</v>
       </c>
       <c r="W6" t="n">
-        <v>2.125661375661375</v>
+        <v>1.277747252747253</v>
       </c>
       <c r="X6" t="n">
-        <v>77.22156084656085</v>
+        <v>72.41016483516484</v>
       </c>
       <c r="Y6" t="n">
-        <v>24202562.83068783</v>
+        <v>6047248.168498168</v>
       </c>
       <c r="Z6" t="n">
-        <v>82.55291005291006</v>
+        <v>78.27152014652015</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fB7pqOjH</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
-        <v>24.3030303030303</v>
-      </c>
-      <c r="D7" t="n">
-        <v>184.7878787878788</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.484848484848485</v>
-      </c>
-      <c r="F7" t="n">
-        <v>76</v>
-      </c>
-      <c r="G7" t="n">
-        <v>11778787.87878788</v>
-      </c>
-      <c r="H7" t="n">
-        <v>79.36363636363636</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>24.85151515151515</v>
+        <v>23.73106060606061</v>
       </c>
       <c r="J7" t="n">
-        <v>184.6727272727273</v>
+        <v>183.1174242424242</v>
       </c>
       <c r="K7" t="n">
-        <v>1.421212121212121</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>74.54545454545455</v>
+        <v>69.09393939393938</v>
       </c>
       <c r="M7" t="n">
-        <v>7250303.03030303</v>
+        <v>2318825.757575757</v>
       </c>
       <c r="N7" t="n">
-        <v>77.9969696969697</v>
-      </c>
-      <c r="O7" t="n">
-        <v>24.92857142857143</v>
-      </c>
-      <c r="P7" t="n">
-        <v>182.8809523809524</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.303571428571429</v>
-      </c>
-      <c r="R7" t="n">
-        <v>70.08333333333333</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4427380.952380952</v>
-      </c>
-      <c r="T7" t="n">
-        <v>74.32142857142857</v>
-      </c>
+        <v>75.30000000000001</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>22.47619047619048</v>
+        <v>22.76438492063492</v>
       </c>
       <c r="V7" t="n">
-        <v>184.0952380952381</v>
+        <v>183.6526124338624</v>
       </c>
       <c r="W7" t="n">
-        <v>1.327380952380953</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>71.98214285714285</v>
+        <v>63.55125661375661</v>
       </c>
       <c r="Y7" t="n">
-        <v>6937797.619047619</v>
+        <v>1168303.571428571</v>
       </c>
       <c r="Z7" t="n">
-        <v>79.00595238095238</v>
+        <v>71.88244047619048</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WWMKlSMu</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
-        <v>26.90909090909091</v>
-      </c>
-      <c r="D8" t="n">
-        <v>184.3030303030303</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.636363636363636</v>
-      </c>
-      <c r="F8" t="n">
-        <v>76.09090909090908</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9112121.212121213</v>
-      </c>
-      <c r="H8" t="n">
-        <v>78.30303030303031</v>
-      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>27.36363636363636</v>
+        <v>26.09166666666667</v>
       </c>
       <c r="J8" t="n">
-        <v>183.5151515151515</v>
+        <v>186.0333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>1.696969696969697</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>75.57575757575758</v>
+        <v>69.375</v>
       </c>
       <c r="M8" t="n">
-        <v>9124242.424242424</v>
+        <v>1829166.666666667</v>
       </c>
       <c r="N8" t="n">
-        <v>77.27272727272727</v>
-      </c>
-      <c r="O8" t="n">
-        <v>27.54166666666667</v>
-      </c>
-      <c r="P8" t="n">
-        <v>184.9953703703704</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.574074074074074</v>
-      </c>
-      <c r="R8" t="n">
-        <v>73.74537037037037</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4630787.037037037</v>
-      </c>
-      <c r="T8" t="n">
-        <v>75.87037037037037</v>
-      </c>
+        <v>73.58333333333333</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>24.15079365079366</v>
+        <v>25.29220085470086</v>
       </c>
       <c r="V8" t="n">
-        <v>185.2222222222223</v>
+        <v>185.292556980057</v>
       </c>
       <c r="W8" t="n">
-        <v>1.34920634920635</v>
+        <v>1.06712962962963</v>
       </c>
       <c r="X8" t="n">
-        <v>72.2936507936508</v>
+        <v>67.18011039886041</v>
       </c>
       <c r="Y8" t="n">
-        <v>3826984.126984127</v>
+        <v>1429728.89957265</v>
       </c>
       <c r="Z8" t="n">
-        <v>76.19047619047619</v>
+        <v>72.81997863247862</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CnIup4yB</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="n">
-        <v>26.18181818181818</v>
-      </c>
-      <c r="D9" t="n">
-        <v>183.0909090909091</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.181818181818182</v>
-      </c>
-      <c r="F9" t="n">
-        <v>73.36363636363636</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4909090.909090909</v>
-      </c>
-      <c r="H9" t="n">
-        <v>76.09090909090909</v>
-      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>27.88888888888889</v>
+        <v>26.95454545454546</v>
       </c>
       <c r="J9" t="n">
-        <v>182.4074074074074</v>
+        <v>184.7045454545455</v>
       </c>
       <c r="K9" t="n">
-        <v>1.259259259259259</v>
+        <v>1.613636363636363</v>
       </c>
       <c r="L9" t="n">
-        <v>73.25925925925925</v>
+        <v>75.83333333333333</v>
       </c>
       <c r="M9" t="n">
-        <v>3616666.666666667</v>
+        <v>8471212.121212121</v>
       </c>
       <c r="N9" t="n">
-        <v>75.03703703703702</v>
-      </c>
-      <c r="O9" t="n">
-        <v>24.82539682539682</v>
-      </c>
-      <c r="P9" t="n">
-        <v>186.2169312169312</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.084656084656085</v>
-      </c>
-      <c r="R9" t="n">
-        <v>66.8888888888889</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1904232.804232804</v>
-      </c>
-      <c r="T9" t="n">
-        <v>72.51322751322751</v>
-      </c>
+        <v>78.16666666666667</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>27.10185185185185</v>
+        <v>27.32126322751323</v>
       </c>
       <c r="V9" t="n">
-        <v>183.8611111111111</v>
+        <v>184.4416335978836</v>
       </c>
       <c r="W9" t="n">
-        <v>1.041666666666667</v>
+        <v>1.525628306878307</v>
       </c>
       <c r="X9" t="n">
-        <v>69.84722222222223</v>
+        <v>73.8738425925926</v>
       </c>
       <c r="Y9" t="n">
-        <v>2045370.37037037</v>
+        <v>5045312.500000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>73.07870370370371</v>
+        <v>75.86044973544975</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>4MEXoQ6b</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>186.7333333333333</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F10" t="n">
-        <v>76.16666666666666</v>
-      </c>
-      <c r="G10" t="n">
-        <v>11725000</v>
-      </c>
-      <c r="H10" t="n">
-        <v>80.03333333333333</v>
-      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>25.75757575757575</v>
+        <v>25.45090909090909</v>
       </c>
       <c r="J10" t="n">
-        <v>183.5757575757576</v>
+        <v>183.8375757575758</v>
       </c>
       <c r="K10" t="n">
-        <v>1.575757575757575</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>74.42424242424242</v>
+        <v>68.32727272727273</v>
       </c>
       <c r="M10" t="n">
-        <v>6700000</v>
+        <v>1664621.212121212</v>
       </c>
       <c r="N10" t="n">
-        <v>78.36363636363637</v>
-      </c>
-      <c r="O10" t="n">
-        <v>25.03703703703703</v>
-      </c>
-      <c r="P10" t="n">
-        <v>183.5555555555555</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.296296296296296</v>
-      </c>
-      <c r="R10" t="n">
-        <v>73.77777777777779</v>
-      </c>
-      <c r="S10" t="n">
-        <v>7732407.407407408</v>
-      </c>
-      <c r="T10" t="n">
-        <v>78.14814814814815</v>
-      </c>
+        <v>71.40000000000001</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>26.29629629629629</v>
+        <v>26.25085542688517</v>
       </c>
       <c r="V10" t="n">
-        <v>185.7407407407407</v>
+        <v>182.0268557042585</v>
       </c>
       <c r="W10" t="n">
-        <v>1.481481481481482</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>71.62962962962962</v>
+        <v>67.49964153356602</v>
       </c>
       <c r="Y10" t="n">
-        <v>3866666.666666667</v>
+        <v>1425058.387074406</v>
       </c>
       <c r="Z10" t="n">
-        <v>75.92592592592594</v>
+        <v>70.55308770388862</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>MZjh9ghT</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>24.86136363636364</v>
+      </c>
+      <c r="J11" t="n">
+        <v>182.7712121212121</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.081818181818182</v>
+      </c>
+      <c r="L11" t="n">
+        <v>80.17954545454546</v>
+      </c>
+      <c r="M11" t="n">
+        <v>28639015.15151516</v>
+      </c>
+      <c r="N11" t="n">
+        <v>83.68712121212121</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="n">
+        <v>25.23296957671957</v>
+      </c>
+      <c r="V11" t="n">
+        <v>185.6076029445595</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.636703473659996</v>
+      </c>
+      <c r="X11" t="n">
+        <v>76.14737893949849</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>15484254.94593973</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>80.69870744191398</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>f1nnRRDE</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25.58671328671329</v>
+      </c>
+      <c r="D12" t="n">
+        <v>183.6125874125874</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>67.12027972027974</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1415332.167832168</v>
+      </c>
+      <c r="H12" t="n">
+        <v>71.00909090909092</v>
+      </c>
+      <c r="I12" t="n">
+        <v>27.25174825174825</v>
+      </c>
+      <c r="J12" t="n">
+        <v>183.6153846153846</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.713286713286713</v>
+      </c>
+      <c r="L12" t="n">
+        <v>75.54545454545453</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9070629.370629372</v>
+      </c>
+      <c r="N12" t="n">
+        <v>77.37062937062936</v>
+      </c>
+      <c r="O12" t="n">
+        <v>26.1256105006105</v>
+      </c>
+      <c r="P12" t="n">
+        <v>184.8692002442002</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>66.59783272283272</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1186095.848595849</v>
+      </c>
+      <c r="T12" t="n">
+        <v>69.75152625152624</v>
+      </c>
+      <c r="U12" t="n">
+        <v>24.84033802454855</v>
+      </c>
+      <c r="V12" t="n">
+        <v>185.1910384936701</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.448115481010218</v>
+      </c>
+      <c r="X12" t="n">
+        <v>73.21261487050961</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>5536173.767752716</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>76.55806182121972</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>8QPARz8c</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>25.92424242424243</v>
+      </c>
+      <c r="J13" t="n">
+        <v>186.5151515151515</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>72.82575757575758</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4325000</v>
+      </c>
+      <c r="N13" t="n">
+        <v>75.07575757575758</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>27.23875661375661</v>
+      </c>
+      <c r="V13" t="n">
+        <v>183.2333002645503</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>68.90112433862434</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1635300.925925926</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>70.67410714285715</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hzyf0b9b</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>25.12878787878788</v>
+      </c>
+      <c r="J14" t="n">
+        <v>186.1590909090909</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="L14" t="n">
+        <v>68.63636363636364</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1782954.545454546</v>
+      </c>
+      <c r="N14" t="n">
+        <v>72.62121212121212</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="n">
+        <v>24.96303485162181</v>
+      </c>
+      <c r="V14" t="n">
+        <v>186.1707930756844</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.007591442374051</v>
+      </c>
+      <c r="X14" t="n">
+        <v>66.23001495284103</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1316034.226190476</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>71.01655595813205</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>CpiTEcOi</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>25.88636363636364</v>
+      </c>
+      <c r="J15" t="n">
+        <v>183.7045454545454</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="L15" t="n">
+        <v>69.7878787878788</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2027462.121212121</v>
+      </c>
+      <c r="N15" t="n">
+        <v>73.78787878787878</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>24.09920634920634</v>
+      </c>
+      <c r="V15" t="n">
+        <v>184.1808862433863</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>66.04050925925925</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1296275.628306878</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>71.49007936507935</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8CpxDyg4</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>25.84090909090909</v>
+      </c>
+      <c r="J16" t="n">
+        <v>184.4318181818182</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.310606060606061</v>
+      </c>
+      <c r="L16" t="n">
+        <v>80.18939393939394</v>
+      </c>
+      <c r="M16" t="n">
+        <v>29079545.45454545</v>
+      </c>
+      <c r="N16" t="n">
+        <v>83.04545454545455</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="n">
+        <v>24.72106481481481</v>
+      </c>
+      <c r="V16" t="n">
+        <v>184.0613425925926</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.925925925925926</v>
+      </c>
+      <c r="X16" t="n">
+        <v>76.91319444444444</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>17697453.70370371</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>82.01041666666667</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6q2yrHgU</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>23.57342657342657</v>
+      </c>
+      <c r="J17" t="n">
+        <v>183.8321678321678</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>67.34965034965035</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1655594.405594406</v>
+      </c>
+      <c r="N17" t="n">
+        <v>73.20979020979021</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="n">
+        <v>26.61635586635587</v>
+      </c>
+      <c r="V17" t="n">
+        <v>182.894425019425</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>66.96950271950271</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1126702.117327117</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>69.7441724941725</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AiJ3kset</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>25.61111111111111</v>
+      </c>
+      <c r="J18" t="n">
+        <v>185.8571548821549</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.467676767676767</v>
+      </c>
+      <c r="L18" t="n">
+        <v>74.52407407407406</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6665492.424242425</v>
+      </c>
+      <c r="N18" t="n">
+        <v>77.1476430976431</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="n">
+        <v>24.26052979671401</v>
+      </c>
+      <c r="V18" t="n">
+        <v>184.0027760373156</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.157494430520746</v>
+      </c>
+      <c r="X18" t="n">
+        <v>71.26524644945698</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3826866.428223337</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>76.35502819548871</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>YV3TqwPH</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>24.09696969696969</v>
+      </c>
+      <c r="J19" t="n">
+        <v>185.5136363636364</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>66.76060606060607</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1471231.060606061</v>
+      </c>
+      <c r="N19" t="n">
+        <v>72.39999999999999</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>24.86836533032185</v>
+      </c>
+      <c r="V19" t="n">
+        <v>186.1097896668549</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>66.78628482025221</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1347329.074910597</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>71.6701075192923</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>l0ueP5rR</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>26.53560606060606</v>
+      </c>
+      <c r="D20" t="n">
+        <v>184.0522727272727</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>67.80909090909091</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1331609.848484848</v>
+      </c>
+      <c r="H20" t="n">
+        <v>70.56060606060606</v>
+      </c>
+      <c r="I20" t="n">
+        <v>23.95227272727273</v>
+      </c>
+      <c r="J20" t="n">
+        <v>184.6340909090909</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L20" t="n">
+        <v>70.46742424242424</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2845984.848484848</v>
+      </c>
+      <c r="N20" t="n">
+        <v>75.64242424242424</v>
+      </c>
+      <c r="O20" t="n">
+        <v>24.94931130664827</v>
+      </c>
+      <c r="P20" t="n">
+        <v>183.5745485392224</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>66.53948844030366</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1217487.275707384</v>
+      </c>
+      <c r="T20" t="n">
+        <v>70.42798194156889</v>
+      </c>
+      <c r="U20" t="n">
+        <v>26.23930372428656</v>
+      </c>
+      <c r="V20" t="n">
+        <v>183.6655943905658</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.239149352850726</v>
+      </c>
+      <c r="X20" t="n">
+        <v>68.87934510188516</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1680755.670880099</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>73.24138849539308</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>t2AoZLAa</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>25.13286713286713</v>
+      </c>
+      <c r="J21" t="n">
+        <v>182.4755244755245</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>67.19580419580419</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1318951.048951049</v>
+      </c>
+      <c r="N21" t="n">
+        <v>70.92307692307692</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>28.06135531135531</v>
+      </c>
+      <c r="V21" t="n">
+        <v>181.1076698155645</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>64.0467868388921</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>712781.6978343294</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>65.57185913501704</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>jFMCm08e</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>27.96444444444445</v>
+      </c>
+      <c r="J22" t="n">
+        <v>183.0874074074074</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.262962962962963</v>
+      </c>
+      <c r="L22" t="n">
+        <v>73.14888888888888</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3618777.777777778</v>
+      </c>
+      <c r="N22" t="n">
+        <v>75.07185185185185</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="n">
+        <v>26.99601503759398</v>
+      </c>
+      <c r="V22" t="n">
+        <v>183.0080785296574</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.042106655527708</v>
+      </c>
+      <c r="X22" t="n">
+        <v>69.90181147312727</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2059198.203842941</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>72.83213032581452</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>tvOIPExA</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>24.41666666666667</v>
+      </c>
+      <c r="J23" t="n">
+        <v>185.1818181818182</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.295454545454546</v>
+      </c>
+      <c r="L23" t="n">
+        <v>72.54545454545455</v>
+      </c>
+      <c r="M23" t="n">
+        <v>5916666.666666667</v>
+      </c>
+      <c r="N23" t="n">
+        <v>77.82575757575758</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="n">
+        <v>26.0925925925926</v>
+      </c>
+      <c r="V23" t="n">
+        <v>185.7731481481481</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.28587962962963</v>
+      </c>
+      <c r="X23" t="n">
+        <v>69.21875</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2556354.166666667</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>74.13194444444444</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>26.13013468013468</v>
+      </c>
+      <c r="J24" t="n">
+        <v>185.9308080808081</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>70.72407407407407</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2406159.511784512</v>
+      </c>
+      <c r="N24" t="n">
+        <v>73.77020202020202</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="n">
+        <v>26.33363526570048</v>
+      </c>
+      <c r="V24" t="n">
+        <v>187.8852297561537</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>68.41533672647803</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1512004.50741891</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>71.24547101449276</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>26.76515151515152</v>
+      </c>
+      <c r="J25" t="n">
+        <v>183.6969696969697</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.015151515151515</v>
+      </c>
+      <c r="L25" t="n">
+        <v>68.82575757575758</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1653598.484848485</v>
+      </c>
+      <c r="N25" t="n">
+        <v>72.91666666666666</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="n">
+        <v>26.71164021164021</v>
+      </c>
+      <c r="V25" t="n">
+        <v>182.818287037037</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.148809523809524</v>
+      </c>
+      <c r="X25" t="n">
+        <v>66.69345238095238</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1143047.288359788</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>71.34705687830687</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>24.60909090909091</v>
+      </c>
+      <c r="J26" t="n">
+        <v>183.4901515151516</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>70.76666666666667</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2784090.909090909</v>
+      </c>
+      <c r="N26" t="n">
+        <v>74.59469696969698</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="n">
+        <v>25.29377104377105</v>
+      </c>
+      <c r="V26" t="n">
+        <v>181.7002765752766</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>69.56464947089948</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2275444.925444926</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>72.93924362674363</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>25.10909090909091</v>
+      </c>
+      <c r="J27" t="n">
+        <v>184.369696969697</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>70.22424242424243</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2589090.909090909</v>
+      </c>
+      <c r="N27" t="n">
+        <v>74.17575757575757</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="n">
+        <v>23.77962962962963</v>
+      </c>
+      <c r="V27" t="n">
+        <v>186.0240740740741</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1633064.814814815</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>72.25648148148149</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>fcxqFy2l</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>25.5560606060606</v>
+      </c>
+      <c r="D28" t="n">
+        <v>184.6888888888889</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.152597402597403</v>
+      </c>
+      <c r="F28" t="n">
+        <v>81.704329004329</v>
+      </c>
+      <c r="G28" t="n">
+        <v>36913708.51370852</v>
+      </c>
+      <c r="H28" t="n">
+        <v>84.44848484848485</v>
+      </c>
+      <c r="I28" t="n">
+        <v>24.35606060606061</v>
+      </c>
+      <c r="J28" t="n">
+        <v>184.7272727272727</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="L28" t="n">
+        <v>76.1969696969697</v>
+      </c>
+      <c r="M28" t="n">
+        <v>11916666.66666666</v>
+      </c>
+      <c r="N28" t="n">
+        <v>79.14393939393939</v>
+      </c>
+      <c r="O28" t="n">
+        <v>23.06161369686215</v>
+      </c>
+      <c r="P28" t="n">
+        <v>182.2996733080584</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.584457933370977</v>
+      </c>
+      <c r="R28" t="n">
+        <v>77.4817092845043</v>
+      </c>
+      <c r="S28" t="n">
+        <v>27706889.09111075</v>
+      </c>
+      <c r="T28" t="n">
+        <v>83.52708014035655</v>
+      </c>
+      <c r="U28" t="n">
+        <v>24.19146825396825</v>
+      </c>
+      <c r="V28" t="n">
+        <v>183.0720899470899</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.242559523809524</v>
+      </c>
+      <c r="X28" t="n">
+        <v>70.49652777777777</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>4968282.903439154</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>75.63210978835978</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/germany/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/p6_deployment/data/germany/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -571,22 +571,22 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>25.93146853146853</v>
+        <v>25.84363636363636</v>
       </c>
       <c r="J2" t="n">
-        <v>184.7412587412588</v>
+        <v>184.6181818181818</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>70.13846153846154</v>
+        <v>70.08363636363637</v>
       </c>
       <c r="M2" t="n">
-        <v>2324195.804195804</v>
+        <v>2310060.606060606</v>
       </c>
       <c r="N2" t="n">
-        <v>73.05314685314686</v>
+        <v>73.09454545454545</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -595,22 +595,22 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>26.21577501445923</v>
+        <v>26.32033834586466</v>
       </c>
       <c r="V2" t="n">
-        <v>185.8954742625795</v>
+        <v>186.0177443609022</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>66.83335743204164</v>
+        <v>66.88057644110276</v>
       </c>
       <c r="Y2" t="n">
-        <v>1262396.616541354</v>
+        <v>1260743.73433584</v>
       </c>
       <c r="Z2" t="n">
-        <v>71.09064488143436</v>
+        <v>70.93689223057645</v>
       </c>
     </row>
     <row r="3">
@@ -623,76 +623,76 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>26.05194805194805</v>
+        <v>25.93048128342246</v>
       </c>
       <c r="D3" t="n">
-        <v>185.6753246753247</v>
+        <v>185.5828877005348</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>67.1103896103896</v>
+        <v>67.12299465240642</v>
       </c>
       <c r="G3" t="n">
-        <v>1187987.012987013</v>
+        <v>1207620.320855615</v>
       </c>
       <c r="H3" t="n">
-        <v>69.59740259740259</v>
+        <v>69.77540106951871</v>
       </c>
       <c r="I3" t="n">
-        <v>25.90151515151515</v>
+        <v>25.88363636363636</v>
       </c>
       <c r="J3" t="n">
-        <v>183.1590909090909</v>
+        <v>183.4181818181818</v>
       </c>
       <c r="K3" t="n">
-        <v>1.598484848484848</v>
+        <v>1.592727272727272</v>
       </c>
       <c r="L3" t="n">
-        <v>74.45454545454545</v>
+        <v>74.4290909090909</v>
       </c>
       <c r="M3" t="n">
-        <v>6766666.666666667</v>
+        <v>6750181.818181817</v>
       </c>
       <c r="N3" t="n">
-        <v>78.35606060606061</v>
+        <v>78.27272727272728</v>
       </c>
       <c r="O3" t="n">
-        <v>24.59821428571428</v>
+        <v>24.63643790849673</v>
       </c>
       <c r="P3" t="n">
-        <v>184.0823412698413</v>
+        <v>184.0024509803922</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>64.85813492063491</v>
+        <v>64.77205882352941</v>
       </c>
       <c r="S3" t="n">
-        <v>977405.753968254</v>
+        <v>957536.7647058824</v>
       </c>
       <c r="T3" t="n">
-        <v>68.78769841269842</v>
+        <v>68.62254901960785</v>
       </c>
       <c r="U3" t="n">
-        <v>25.84755291005291</v>
+        <v>26.10392546583851</v>
       </c>
       <c r="V3" t="n">
-        <v>184.9790013227513</v>
+        <v>184.7884375431332</v>
       </c>
       <c r="W3" t="n">
-        <v>1.465608465608466</v>
+        <v>1.496536231884058</v>
       </c>
       <c r="X3" t="n">
-        <v>71.76984126984127</v>
+        <v>72.19923188405797</v>
       </c>
       <c r="Y3" t="n">
-        <v>4261069.775132275</v>
+        <v>4507439.320220841</v>
       </c>
       <c r="Z3" t="n">
-        <v>76.27976190476191</v>
+        <v>76.34969082125603</v>
       </c>
     </row>
     <row r="4">
@@ -711,22 +711,22 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>26.5530303030303</v>
+        <v>26.43181818181818</v>
       </c>
       <c r="J4" t="n">
-        <v>185.8787878787879</v>
+        <v>185.7916666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>1.795454545454545</v>
+        <v>1.78030303030303</v>
       </c>
       <c r="L4" t="n">
-        <v>75.31060606060606</v>
+        <v>75.21590909090908</v>
       </c>
       <c r="M4" t="n">
-        <v>8715151.515151516</v>
+        <v>8631818.181818182</v>
       </c>
       <c r="N4" t="n">
-        <v>78.81818181818183</v>
+        <v>78.88257575757576</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -735,22 +735,22 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>24.07903439153439</v>
+        <v>24.32393389118932</v>
       </c>
       <c r="V4" t="n">
-        <v>185.0983796296296</v>
+        <v>184.7463804060272</v>
       </c>
       <c r="W4" t="n">
-        <v>1.308531746031746</v>
+        <v>1.346938262019783</v>
       </c>
       <c r="X4" t="n">
-        <v>70.4890873015873</v>
+        <v>70.98909449045318</v>
       </c>
       <c r="Y4" t="n">
-        <v>4545899.470899471</v>
+        <v>4994844.414970095</v>
       </c>
       <c r="Z4" t="n">
-        <v>77.3587962962963</v>
+        <v>77.42874036691971</v>
       </c>
     </row>
     <row r="5">
@@ -769,22 +769,22 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>27.18181818181818</v>
+        <v>27.18560606060606</v>
       </c>
       <c r="J5" t="n">
-        <v>185.0419580419581</v>
+        <v>185.1931818181818</v>
       </c>
       <c r="K5" t="n">
-        <v>3.146853146853147</v>
+        <v>3.143939393939394</v>
       </c>
       <c r="L5" t="n">
-        <v>82.37762237762239</v>
+        <v>82.46969696969698</v>
       </c>
       <c r="M5" t="n">
-        <v>44731993.00699301</v>
+        <v>45745265.15151515</v>
       </c>
       <c r="N5" t="n">
-        <v>84.96503496503496</v>
+        <v>84.97727272727273</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -793,22 +793,22 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>24.63843101343101</v>
+        <v>24.87941074758151</v>
       </c>
       <c r="V5" t="n">
-        <v>182.2466422466422</v>
+        <v>182.0659746643728</v>
       </c>
       <c r="W5" t="n">
-        <v>2.005494505494505</v>
+        <v>2.147727117943079</v>
       </c>
       <c r="X5" t="n">
-        <v>77.13530219780219</v>
+        <v>77.91587622678512</v>
       </c>
       <c r="Y5" t="n">
-        <v>23187456.12026862</v>
+        <v>26298143.27481081</v>
       </c>
       <c r="Z5" t="n">
-        <v>82.6941391941392</v>
+        <v>83.04825326725356</v>
       </c>
     </row>
     <row r="6">
@@ -827,22 +827,22 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>24.97855477855478</v>
+        <v>24.84925252525252</v>
       </c>
       <c r="J6" t="n">
-        <v>184.7278943278943</v>
+        <v>184.8076767676768</v>
       </c>
       <c r="K6" t="n">
-        <v>1.500621600621601</v>
+        <v>1.49220202020202</v>
       </c>
       <c r="L6" t="n">
-        <v>75.24040404040404</v>
+        <v>75.25357575757576</v>
       </c>
       <c r="M6" t="n">
-        <v>8566565.656565655</v>
+        <v>8616650.505050505</v>
       </c>
       <c r="N6" t="n">
-        <v>78.22665112665113</v>
+        <v>78.27482828282828</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -851,22 +851,22 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>23.23699633699633</v>
+        <v>23.43553056554429</v>
       </c>
       <c r="V6" t="n">
-        <v>183.7899267399267</v>
+        <v>183.4115297482838</v>
       </c>
       <c r="W6" t="n">
-        <v>1.277747252747253</v>
+        <v>1.295255403000254</v>
       </c>
       <c r="X6" t="n">
-        <v>72.41016483516484</v>
+        <v>72.71196026297628</v>
       </c>
       <c r="Y6" t="n">
-        <v>6047248.168498168</v>
+        <v>6241387.857324472</v>
       </c>
       <c r="Z6" t="n">
-        <v>78.27152014652015</v>
+        <v>78.22619705059751</v>
       </c>
     </row>
     <row r="7">
@@ -885,22 +885,22 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>23.73106060606061</v>
+        <v>23.73030303030303</v>
       </c>
       <c r="J7" t="n">
-        <v>183.1174242424242</v>
+        <v>183.2090909090909</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>69.09393939393938</v>
+        <v>69.14181818181818</v>
       </c>
       <c r="M7" t="n">
-        <v>2318825.757575757</v>
+        <v>2332030.303030303</v>
       </c>
       <c r="N7" t="n">
-        <v>75.30000000000001</v>
+        <v>75.36121212121212</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -909,22 +909,22 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>22.76438492063492</v>
+        <v>22.88650793650794</v>
       </c>
       <c r="V7" t="n">
-        <v>183.6526124338624</v>
+        <v>183.4554232804233</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>63.55125661375661</v>
+        <v>63.91600529100528</v>
       </c>
       <c r="Y7" t="n">
-        <v>1168303.571428571</v>
+        <v>1211101.190476191</v>
       </c>
       <c r="Z7" t="n">
-        <v>71.88244047619048</v>
+        <v>71.86428571428571</v>
       </c>
     </row>
     <row r="8">
@@ -943,22 +943,22 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>26.09166666666667</v>
+        <v>26.28</v>
       </c>
       <c r="J8" t="n">
-        <v>186.0333333333333</v>
+        <v>185.8266666666667</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>69.375</v>
+        <v>69.52666666666667</v>
       </c>
       <c r="M8" t="n">
-        <v>1829166.666666667</v>
+        <v>1836666.666666667</v>
       </c>
       <c r="N8" t="n">
-        <v>73.58333333333333</v>
+        <v>73.32666666666667</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -967,22 +967,22 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>25.29220085470086</v>
+        <v>25.59672364672365</v>
       </c>
       <c r="V8" t="n">
-        <v>185.292556980057</v>
+        <v>185.5155270655271</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06712962962963</v>
+        <v>1.075925925925926</v>
       </c>
       <c r="X8" t="n">
-        <v>67.18011039886041</v>
+        <v>67.41816239316239</v>
       </c>
       <c r="Y8" t="n">
-        <v>1429728.89957265</v>
+        <v>1430449.786324786</v>
       </c>
       <c r="Z8" t="n">
-        <v>72.81997863247862</v>
+        <v>72.78931623931622</v>
       </c>
     </row>
     <row r="9">
@@ -1001,22 +1001,22 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>26.95454545454546</v>
+        <v>27.01090909090909</v>
       </c>
       <c r="J9" t="n">
-        <v>184.7045454545455</v>
+        <v>184.9454545454546</v>
       </c>
       <c r="K9" t="n">
-        <v>1.613636363636363</v>
+        <v>1.629090909090909</v>
       </c>
       <c r="L9" t="n">
-        <v>75.83333333333333</v>
+        <v>75.80727272727273</v>
       </c>
       <c r="M9" t="n">
-        <v>8471212.121212121</v>
+        <v>8416181.818181818</v>
       </c>
       <c r="N9" t="n">
-        <v>78.16666666666667</v>
+        <v>78.08000000000001</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -1025,22 +1025,22 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>27.32126322751323</v>
+        <v>26.84057934691802</v>
       </c>
       <c r="V9" t="n">
-        <v>184.4416335978836</v>
+        <v>183.9944046710981</v>
       </c>
       <c r="W9" t="n">
-        <v>1.525628306878307</v>
+        <v>1.480745523228361</v>
       </c>
       <c r="X9" t="n">
-        <v>73.8738425925926</v>
+        <v>73.74021230612765</v>
       </c>
       <c r="Y9" t="n">
-        <v>5045312.500000001</v>
+        <v>5214261.759471141</v>
       </c>
       <c r="Z9" t="n">
-        <v>75.86044973544975</v>
+        <v>76.13055464748828</v>
       </c>
     </row>
     <row r="10">
@@ -1059,22 +1059,22 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>25.45090909090909</v>
+        <v>25.27979797979798</v>
       </c>
       <c r="J10" t="n">
-        <v>183.8375757575758</v>
+        <v>183.9555555555555</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>68.32727272727273</v>
+        <v>68.37878787878789</v>
       </c>
       <c r="M10" t="n">
-        <v>1664621.212121212</v>
+        <v>1701830.808080808</v>
       </c>
       <c r="N10" t="n">
-        <v>71.40000000000001</v>
+        <v>71.61111111111111</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -1083,22 +1083,22 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>26.25085542688517</v>
+        <v>26.1187684112932</v>
       </c>
       <c r="V10" t="n">
-        <v>182.0268557042585</v>
+        <v>182.0825649387339</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>67.49964153356602</v>
+        <v>67.475009919947</v>
       </c>
       <c r="Y10" t="n">
-        <v>1425058.387074406</v>
+        <v>1445442.174413857</v>
       </c>
       <c r="Z10" t="n">
-        <v>70.55308770388862</v>
+        <v>70.65766567916643</v>
       </c>
     </row>
     <row r="11">
@@ -1117,22 +1117,22 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>24.86136363636364</v>
+        <v>25.01515151515152</v>
       </c>
       <c r="J11" t="n">
-        <v>182.7712121212121</v>
+        <v>182.7034090909091</v>
       </c>
       <c r="K11" t="n">
-        <v>2.081818181818182</v>
+        <v>2.114772727272727</v>
       </c>
       <c r="L11" t="n">
-        <v>80.17954545454546</v>
+        <v>80.2594696969697</v>
       </c>
       <c r="M11" t="n">
-        <v>28639015.15151516</v>
+        <v>28676704.54545455</v>
       </c>
       <c r="N11" t="n">
-        <v>83.68712121212121</v>
+        <v>83.63409090909092</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -1141,22 +1141,22 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
-        <v>25.23296957671957</v>
+        <v>24.78276685070163</v>
       </c>
       <c r="V11" t="n">
-        <v>185.6076029445595</v>
+        <v>185.307395905222</v>
       </c>
       <c r="W11" t="n">
-        <v>1.636703473659996</v>
+        <v>1.666533672647803</v>
       </c>
       <c r="X11" t="n">
-        <v>76.14737893949849</v>
+        <v>76.70394453071084</v>
       </c>
       <c r="Y11" t="n">
-        <v>15484254.94593973</v>
+        <v>17697117.9836669</v>
       </c>
       <c r="Z11" t="n">
-        <v>80.69870744191398</v>
+        <v>81.43627070393374</v>
       </c>
     </row>
     <row r="12">
@@ -1169,76 +1169,76 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>25.58671328671329</v>
+        <v>25.55090909090909</v>
       </c>
       <c r="D12" t="n">
-        <v>183.6125874125874</v>
+        <v>183.4945454545455</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>67.12027972027974</v>
+        <v>67.17090909090909</v>
       </c>
       <c r="G12" t="n">
-        <v>1415332.167832168</v>
+        <v>1433590.909090909</v>
       </c>
       <c r="H12" t="n">
-        <v>71.00909090909092</v>
+        <v>71.06242424242424</v>
       </c>
       <c r="I12" t="n">
-        <v>27.25174825174825</v>
+        <v>27.23484848484849</v>
       </c>
       <c r="J12" t="n">
-        <v>183.6153846153846</v>
+        <v>183.7840909090909</v>
       </c>
       <c r="K12" t="n">
-        <v>1.713286713286713</v>
+        <v>1.712121212121212</v>
       </c>
       <c r="L12" t="n">
-        <v>75.54545454545453</v>
+        <v>75.54924242424242</v>
       </c>
       <c r="M12" t="n">
-        <v>9070629.370629372</v>
+        <v>9118181.818181818</v>
       </c>
       <c r="N12" t="n">
-        <v>77.37062937062936</v>
+        <v>77.40151515151516</v>
       </c>
       <c r="O12" t="n">
-        <v>26.1256105006105</v>
+        <v>26.20886243386243</v>
       </c>
       <c r="P12" t="n">
-        <v>184.8692002442002</v>
+        <v>185.1949735449735</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>66.59783272283272</v>
+        <v>66.5681216931217</v>
       </c>
       <c r="S12" t="n">
-        <v>1186095.848595849</v>
+        <v>1171283.068783069</v>
       </c>
       <c r="T12" t="n">
-        <v>69.75152625152624</v>
+        <v>69.75132275132275</v>
       </c>
       <c r="U12" t="n">
-        <v>24.84033802454855</v>
+        <v>24.99484444807672</v>
       </c>
       <c r="V12" t="n">
-        <v>185.1910384936701</v>
+        <v>184.9159408560653</v>
       </c>
       <c r="W12" t="n">
-        <v>1.448115481010218</v>
+        <v>1.470589479435303</v>
       </c>
       <c r="X12" t="n">
-        <v>73.21261487050961</v>
+        <v>73.55038975003936</v>
       </c>
       <c r="Y12" t="n">
-        <v>5536173.767752716</v>
+        <v>6272273.95367949</v>
       </c>
       <c r="Z12" t="n">
-        <v>76.55806182121972</v>
+        <v>76.75503260339859</v>
       </c>
     </row>
     <row r="13">
@@ -1257,22 +1257,22 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>25.92424242424243</v>
+        <v>25.89015151515151</v>
       </c>
       <c r="J13" t="n">
-        <v>186.5151515151515</v>
+        <v>186.7159090909091</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>72.82575757575758</v>
+        <v>72.85606060606061</v>
       </c>
       <c r="M13" t="n">
-        <v>4325000</v>
+        <v>4351988.636363637</v>
       </c>
       <c r="N13" t="n">
-        <v>75.07575757575758</v>
+        <v>75.10606060606061</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -1281,22 +1281,22 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>27.23875661375661</v>
+        <v>27.16863641591902</v>
       </c>
       <c r="V13" t="n">
-        <v>183.2333002645503</v>
+        <v>182.88109615827</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>68.90112433862434</v>
+        <v>69.30280581435473</v>
       </c>
       <c r="Y13" t="n">
-        <v>1635300.925925926</v>
+        <v>1835307.126322751</v>
       </c>
       <c r="Z13" t="n">
-        <v>70.67410714285715</v>
+        <v>71.03622469519208</v>
       </c>
     </row>
     <row r="14">
@@ -1315,22 +1315,22 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>25.12878787878788</v>
+        <v>25.13939393939394</v>
       </c>
       <c r="J14" t="n">
-        <v>186.1590909090909</v>
+        <v>186.0848484848485</v>
       </c>
       <c r="K14" t="n">
-        <v>1.083333333333333</v>
+        <v>1.078787878787879</v>
       </c>
       <c r="L14" t="n">
-        <v>68.63636363636364</v>
+        <v>68.64242424242424</v>
       </c>
       <c r="M14" t="n">
-        <v>1782954.545454546</v>
+        <v>1786969.696969697</v>
       </c>
       <c r="N14" t="n">
-        <v>72.62121212121212</v>
+        <v>72.60606060606059</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -1339,22 +1339,22 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
-        <v>24.96303485162181</v>
+        <v>24.97135380722337</v>
       </c>
       <c r="V14" t="n">
-        <v>186.1707930756844</v>
+        <v>186.3218196457327</v>
       </c>
       <c r="W14" t="n">
-        <v>1.007591442374051</v>
+        <v>1.006073153899241</v>
       </c>
       <c r="X14" t="n">
-        <v>66.23001495284103</v>
+        <v>66.1043823326432</v>
       </c>
       <c r="Y14" t="n">
-        <v>1316034.226190476</v>
+        <v>1264679.232804233</v>
       </c>
       <c r="Z14" t="n">
-        <v>71.01655595813205</v>
+        <v>70.90954106280194</v>
       </c>
     </row>
     <row r="15">
@@ -1373,22 +1373,22 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>25.88636363636364</v>
+        <v>25.90909090909091</v>
       </c>
       <c r="J15" t="n">
-        <v>183.7045454545454</v>
+        <v>183.6121212121212</v>
       </c>
       <c r="K15" t="n">
-        <v>1.181818181818182</v>
+        <v>1.16969696969697</v>
       </c>
       <c r="L15" t="n">
-        <v>69.7878787878788</v>
+        <v>69.7818181818182</v>
       </c>
       <c r="M15" t="n">
-        <v>2027462.121212121</v>
+        <v>2006363.636363636</v>
       </c>
       <c r="N15" t="n">
-        <v>73.78787878787878</v>
+        <v>73.73333333333333</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -1397,22 +1397,22 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>24.09920634920634</v>
+        <v>24.07195767195767</v>
       </c>
       <c r="V15" t="n">
-        <v>184.1808862433863</v>
+        <v>184.3002645502646</v>
       </c>
       <c r="W15" t="n">
         <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>66.04050925925925</v>
+        <v>66.04722222222222</v>
       </c>
       <c r="Y15" t="n">
-        <v>1296275.628306878</v>
+        <v>1300539.021164021</v>
       </c>
       <c r="Z15" t="n">
-        <v>71.49007936507935</v>
+        <v>71.710582010582</v>
       </c>
     </row>
     <row r="16">
@@ -1431,22 +1431,22 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>25.84090909090909</v>
+        <v>25.80681818181818</v>
       </c>
       <c r="J16" t="n">
-        <v>184.4318181818182</v>
+        <v>184.4621212121212</v>
       </c>
       <c r="K16" t="n">
-        <v>2.310606060606061</v>
+        <v>2.321969696969697</v>
       </c>
       <c r="L16" t="n">
-        <v>80.18939393939394</v>
+        <v>80.24621212121212</v>
       </c>
       <c r="M16" t="n">
-        <v>29079545.45454545</v>
+        <v>29456060.60606061</v>
       </c>
       <c r="N16" t="n">
-        <v>83.04545454545455</v>
+        <v>83.11742424242425</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -1455,22 +1455,22 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="n">
-        <v>24.72106481481481</v>
+        <v>24.83647486772487</v>
       </c>
       <c r="V16" t="n">
-        <v>184.0613425925926</v>
+        <v>183.855076058201</v>
       </c>
       <c r="W16" t="n">
-        <v>1.925925925925926</v>
+        <v>1.949900793650794</v>
       </c>
       <c r="X16" t="n">
-        <v>76.91319444444444</v>
+        <v>77.17939814814815</v>
       </c>
       <c r="Y16" t="n">
-        <v>17697453.70370371</v>
+        <v>18144204.6957672</v>
       </c>
       <c r="Z16" t="n">
-        <v>82.01041666666667</v>
+        <v>82.01909722222221</v>
       </c>
     </row>
     <row r="17">
@@ -1489,22 +1489,22 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>23.57342657342657</v>
+        <v>23.75151515151515</v>
       </c>
       <c r="J17" t="n">
-        <v>183.8321678321678</v>
+        <v>183.9030303030303</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>67.34965034965035</v>
+        <v>67.47272727272727</v>
       </c>
       <c r="M17" t="n">
-        <v>1655594.405594406</v>
+        <v>1659090.909090909</v>
       </c>
       <c r="N17" t="n">
-        <v>73.20979020979021</v>
+        <v>73.03636363636363</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -1513,22 +1513,22 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="n">
-        <v>26.61635586635587</v>
+        <v>26.40824915824916</v>
       </c>
       <c r="V17" t="n">
-        <v>182.894425019425</v>
+        <v>183.167760942761</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>66.96950271950271</v>
+        <v>66.72912457912459</v>
       </c>
       <c r="Y17" t="n">
-        <v>1126702.117327117</v>
+        <v>1104993.686868687</v>
       </c>
       <c r="Z17" t="n">
-        <v>69.7441724941725</v>
+        <v>69.79309764309764</v>
       </c>
     </row>
     <row r="18">
@@ -1547,22 +1547,22 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>25.61111111111111</v>
+        <v>25.65046296296296</v>
       </c>
       <c r="J18" t="n">
-        <v>185.8571548821549</v>
+        <v>185.8619107744108</v>
       </c>
       <c r="K18" t="n">
-        <v>1.467676767676767</v>
+        <v>1.45976430976431</v>
       </c>
       <c r="L18" t="n">
-        <v>74.52407407407406</v>
+        <v>74.625</v>
       </c>
       <c r="M18" t="n">
-        <v>6665492.424242425</v>
+        <v>6710662.878787879</v>
       </c>
       <c r="N18" t="n">
-        <v>77.1476430976431</v>
+        <v>77.19234006734007</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -1571,22 +1571,22 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="n">
-        <v>24.26052979671401</v>
+        <v>24.30819129718607</v>
       </c>
       <c r="V18" t="n">
-        <v>184.0027760373156</v>
+        <v>183.6187468960205</v>
       </c>
       <c r="W18" t="n">
-        <v>1.157494430520746</v>
+        <v>1.147585874129024</v>
       </c>
       <c r="X18" t="n">
-        <v>71.26524644945698</v>
+        <v>71.62761588453829</v>
       </c>
       <c r="Y18" t="n">
-        <v>3826866.428223337</v>
+        <v>4006952.868060768</v>
       </c>
       <c r="Z18" t="n">
-        <v>76.35502819548871</v>
+        <v>76.3987690673691</v>
       </c>
     </row>
     <row r="19">
@@ -1605,22 +1605,22 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>24.09696969696969</v>
+        <v>24.03515151515152</v>
       </c>
       <c r="J19" t="n">
-        <v>185.5136363636364</v>
+        <v>185.7927272727273</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>66.76060606060607</v>
+        <v>66.72363636363637</v>
       </c>
       <c r="M19" t="n">
-        <v>1471231.060606061</v>
+        <v>1459409.090909091</v>
       </c>
       <c r="N19" t="n">
-        <v>72.39999999999999</v>
+        <v>72.31393939393939</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -1629,22 +1629,22 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="n">
-        <v>24.86836533032185</v>
+        <v>24.71506263462785</v>
       </c>
       <c r="V19" t="n">
-        <v>186.1097896668549</v>
+        <v>185.7294984001506</v>
       </c>
       <c r="W19" t="n">
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>66.78628482025221</v>
+        <v>66.6373611895351</v>
       </c>
       <c r="Y19" t="n">
-        <v>1347329.074910597</v>
+        <v>1347724.371039589</v>
       </c>
       <c r="Z19" t="n">
-        <v>71.6701075192923</v>
+        <v>71.76849342284125</v>
       </c>
     </row>
     <row r="20">
@@ -1657,76 +1657,76 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>26.53560606060606</v>
+        <v>26.54969696969697</v>
       </c>
       <c r="D20" t="n">
-        <v>184.0522727272727</v>
+        <v>184.3387878787879</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>67.80909090909091</v>
+        <v>67.76242424242425</v>
       </c>
       <c r="G20" t="n">
-        <v>1331609.848484848</v>
+        <v>1327106.060606061</v>
       </c>
       <c r="H20" t="n">
-        <v>70.56060606060606</v>
+        <v>70.56363636363636</v>
       </c>
       <c r="I20" t="n">
-        <v>23.95227272727273</v>
+        <v>24.26306818181818</v>
       </c>
       <c r="J20" t="n">
-        <v>184.6340909090909</v>
+        <v>184.7460227272728</v>
       </c>
       <c r="K20" t="n">
-        <v>1.05</v>
+        <v>1.073863636363636</v>
       </c>
       <c r="L20" t="n">
-        <v>70.46742424242424</v>
+        <v>70.53920454545454</v>
       </c>
       <c r="M20" t="n">
-        <v>2845984.848484848</v>
+        <v>2805454.545454545</v>
       </c>
       <c r="N20" t="n">
-        <v>75.64242424242424</v>
+        <v>75.48295454545455</v>
       </c>
       <c r="O20" t="n">
-        <v>24.94931130664827</v>
+        <v>24.73087761674718</v>
       </c>
       <c r="P20" t="n">
-        <v>183.5745485392224</v>
+        <v>183.3894007361399</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>66.53948844030366</v>
+        <v>66.39468599033816</v>
       </c>
       <c r="S20" t="n">
-        <v>1217487.275707384</v>
+        <v>1208483.868184955</v>
       </c>
       <c r="T20" t="n">
-        <v>70.42798194156889</v>
+        <v>70.55429031515989</v>
       </c>
       <c r="U20" t="n">
-        <v>26.23930372428656</v>
+        <v>25.91930914242127</v>
       </c>
       <c r="V20" t="n">
-        <v>183.6655943905658</v>
+        <v>183.1085707929244</v>
       </c>
       <c r="W20" t="n">
-        <v>1.239149352850726</v>
+        <v>1.209991974955505</v>
       </c>
       <c r="X20" t="n">
-        <v>68.87934510188516</v>
+        <v>68.57220723911227</v>
       </c>
       <c r="Y20" t="n">
-        <v>1680755.670880099</v>
+        <v>1682609.16387436</v>
       </c>
       <c r="Z20" t="n">
-        <v>73.24138849539308</v>
+        <v>73.19443422868767</v>
       </c>
     </row>
     <row r="21">
@@ -1745,22 +1745,22 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>25.13286713286713</v>
+        <v>25.08484848484848</v>
       </c>
       <c r="J21" t="n">
-        <v>182.4755244755245</v>
+        <v>182.4909090909091</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>67.19580419580419</v>
+        <v>67.2909090909091</v>
       </c>
       <c r="M21" t="n">
-        <v>1318951.048951049</v>
+        <v>1338393.93939394</v>
       </c>
       <c r="N21" t="n">
-        <v>70.92307692307692</v>
+        <v>70.96969696969697</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -1769,22 +1769,22 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
-        <v>28.06135531135531</v>
+        <v>27.9031746031746</v>
       </c>
       <c r="V21" t="n">
-        <v>181.1076698155645</v>
+        <v>181.1016471734893</v>
       </c>
       <c r="W21" t="n">
         <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>64.0467868388921</v>
+        <v>64.24054859370649</v>
       </c>
       <c r="Y21" t="n">
-        <v>712781.6978343294</v>
+        <v>731285.8047897521</v>
       </c>
       <c r="Z21" t="n">
-        <v>65.57185913501704</v>
+        <v>65.70394458368143</v>
       </c>
     </row>
     <row r="22">
@@ -1803,22 +1803,22 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>27.96444444444445</v>
+        <v>27.92777777777778</v>
       </c>
       <c r="J22" t="n">
-        <v>183.0874074074074</v>
+        <v>183.1965811965812</v>
       </c>
       <c r="K22" t="n">
-        <v>1.262962962962963</v>
+        <v>1.265811965811966</v>
       </c>
       <c r="L22" t="n">
-        <v>73.14888888888888</v>
+        <v>73.1794871794872</v>
       </c>
       <c r="M22" t="n">
-        <v>3618777.777777778</v>
+        <v>3630032.051282051</v>
       </c>
       <c r="N22" t="n">
-        <v>75.07185185185185</v>
+        <v>75.15897435897435</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
@@ -1827,22 +1827,22 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="n">
-        <v>26.99601503759398</v>
+        <v>26.73745421245421</v>
       </c>
       <c r="V22" t="n">
-        <v>183.0080785296574</v>
+        <v>182.4158289460349</v>
       </c>
       <c r="W22" t="n">
-        <v>1.042106655527708</v>
+        <v>1.04545714900406</v>
       </c>
       <c r="X22" t="n">
-        <v>69.90181147312727</v>
+        <v>70.09494745973578</v>
       </c>
       <c r="Y22" t="n">
-        <v>2059198.203842941</v>
+        <v>2184121.574697233</v>
       </c>
       <c r="Z22" t="n">
-        <v>72.83213032581452</v>
+        <v>73.0017850665734</v>
       </c>
     </row>
     <row r="23">
@@ -1861,22 +1861,22 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>24.41666666666667</v>
+        <v>24.37878787878788</v>
       </c>
       <c r="J23" t="n">
-        <v>185.1818181818182</v>
+        <v>185.1439393939394</v>
       </c>
       <c r="K23" t="n">
         <v>1.295454545454546</v>
       </c>
       <c r="L23" t="n">
-        <v>72.54545454545455</v>
+        <v>72.5719696969697</v>
       </c>
       <c r="M23" t="n">
-        <v>5916666.666666667</v>
+        <v>5912878.787878788</v>
       </c>
       <c r="N23" t="n">
-        <v>77.82575757575758</v>
+        <v>77.85606060606061</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -1885,22 +1885,22 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="n">
-        <v>26.0925925925926</v>
+        <v>25.79629629629629</v>
       </c>
       <c r="V23" t="n">
-        <v>185.7731481481481</v>
+        <v>185.338210978836</v>
       </c>
       <c r="W23" t="n">
-        <v>1.28587962962963</v>
+        <v>1.261739417989418</v>
       </c>
       <c r="X23" t="n">
-        <v>69.21875</v>
+        <v>69.37003968253968</v>
       </c>
       <c r="Y23" t="n">
-        <v>2556354.166666667</v>
+        <v>2715412.533068783</v>
       </c>
       <c r="Z23" t="n">
-        <v>74.13194444444444</v>
+        <v>74.37838955026456</v>
       </c>
     </row>
     <row r="24">
@@ -1919,22 +1919,22 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>26.13013468013468</v>
+        <v>26.21919191919192</v>
       </c>
       <c r="J24" t="n">
-        <v>185.9308080808081</v>
+        <v>185.9505892255892</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>70.72407407407407</v>
+        <v>70.73985690235691</v>
       </c>
       <c r="M24" t="n">
-        <v>2406159.511784512</v>
+        <v>2382124.368686868</v>
       </c>
       <c r="N24" t="n">
-        <v>73.77020202020202</v>
+        <v>73.69482323232323</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
@@ -1943,22 +1943,22 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="n">
-        <v>26.33363526570048</v>
+        <v>26.09022927407678</v>
       </c>
       <c r="V24" t="n">
-        <v>187.8852297561537</v>
+        <v>187.1591262652404</v>
       </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>68.41533672647803</v>
+        <v>68.58049072890024</v>
       </c>
       <c r="Y24" t="n">
-        <v>1512004.50741891</v>
+        <v>1616511.003404985</v>
       </c>
       <c r="Z24" t="n">
-        <v>71.24547101449276</v>
+        <v>71.57790316005629</v>
       </c>
     </row>
     <row r="25">
@@ -1977,22 +1977,22 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>26.76515151515152</v>
+        <v>27.00606060606061</v>
       </c>
       <c r="J25" t="n">
-        <v>183.6969696969697</v>
+        <v>183.7333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>1.015151515151515</v>
+        <v>1.012121212121212</v>
       </c>
       <c r="L25" t="n">
-        <v>68.82575757575758</v>
+        <v>68.92121212121212</v>
       </c>
       <c r="M25" t="n">
-        <v>1653598.484848485</v>
+        <v>1640000</v>
       </c>
       <c r="N25" t="n">
-        <v>72.91666666666666</v>
+        <v>72.76363636363635</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -2001,22 +2001,22 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="n">
-        <v>26.71164021164021</v>
+        <v>26.53968253968254</v>
       </c>
       <c r="V25" t="n">
-        <v>182.818287037037</v>
+        <v>183.0027777777777</v>
       </c>
       <c r="W25" t="n">
-        <v>1.148809523809524</v>
+        <v>1.119047619047619</v>
       </c>
       <c r="X25" t="n">
-        <v>66.69345238095238</v>
+        <v>66.70291005291006</v>
       </c>
       <c r="Y25" t="n">
-        <v>1143047.288359788</v>
+        <v>1142956.349206349</v>
       </c>
       <c r="Z25" t="n">
-        <v>71.34705687830687</v>
+        <v>71.3739417989418</v>
       </c>
     </row>
     <row r="26">
@@ -2035,22 +2035,22 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>24.60909090909091</v>
+        <v>24.6569696969697</v>
       </c>
       <c r="J26" t="n">
-        <v>183.4901515151516</v>
+        <v>183.4224242424243</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>70.76666666666667</v>
+        <v>70.77696969696969</v>
       </c>
       <c r="M26" t="n">
-        <v>2784090.909090909</v>
+        <v>2776363.636363636</v>
       </c>
       <c r="N26" t="n">
-        <v>74.59469696969698</v>
+        <v>74.53636363636363</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
@@ -2059,22 +2059,22 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="n">
-        <v>25.29377104377105</v>
+        <v>25.16001683501684</v>
       </c>
       <c r="V26" t="n">
-        <v>181.7002765752766</v>
+        <v>181.9852212602213</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>69.56464947089948</v>
+        <v>69.51005291005292</v>
       </c>
       <c r="Y26" t="n">
-        <v>2275444.925444926</v>
+        <v>2252022.607022607</v>
       </c>
       <c r="Z26" t="n">
-        <v>72.93924362674363</v>
+        <v>73.00972823472824</v>
       </c>
     </row>
     <row r="27">
@@ -2093,22 +2093,22 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>25.10909090909091</v>
+        <v>25.11111111111111</v>
       </c>
       <c r="J27" t="n">
-        <v>184.369696969697</v>
+        <v>184.4848484848485</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>70.22424242424243</v>
+        <v>70.1919191919192</v>
       </c>
       <c r="M27" t="n">
-        <v>2589090.909090909</v>
+        <v>2569696.96969697</v>
       </c>
       <c r="N27" t="n">
-        <v>74.17575757575757</v>
+        <v>74.17676767676767</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -2117,22 +2117,22 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="n">
-        <v>23.77962962962963</v>
+        <v>23.50694444444444</v>
       </c>
       <c r="V27" t="n">
-        <v>186.0240740740741</v>
+        <v>186.0601851851852</v>
       </c>
       <c r="W27" t="n">
         <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>66.66666666666667</v>
+        <v>66.11882716049382</v>
       </c>
       <c r="Y27" t="n">
-        <v>1633064.814814815</v>
+        <v>1558275.462962963</v>
       </c>
       <c r="Z27" t="n">
-        <v>72.25648148148149</v>
+        <v>72.07793209876543</v>
       </c>
     </row>
     <row r="28">
@@ -2145,76 +2145,76 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>25.5560606060606</v>
+        <v>25.53430602319492</v>
       </c>
       <c r="D28" t="n">
-        <v>184.6888888888889</v>
+        <v>184.4677141788253</v>
       </c>
       <c r="E28" t="n">
-        <v>2.152597402597403</v>
+        <v>2.169322858211747</v>
       </c>
       <c r="F28" t="n">
-        <v>81.704329004329</v>
+        <v>81.66719042274597</v>
       </c>
       <c r="G28" t="n">
-        <v>36913708.51370852</v>
+        <v>37101945.37972316</v>
       </c>
       <c r="H28" t="n">
-        <v>84.44848484848485</v>
+        <v>84.42667414889638</v>
       </c>
       <c r="I28" t="n">
-        <v>24.35606060606061</v>
+        <v>24.39272727272727</v>
       </c>
       <c r="J28" t="n">
         <v>184.7272727272727</v>
       </c>
       <c r="K28" t="n">
-        <v>1.545454545454545</v>
+        <v>1.534545454545454</v>
       </c>
       <c r="L28" t="n">
-        <v>76.1969696969697</v>
+        <v>76.11272727272728</v>
       </c>
       <c r="M28" t="n">
-        <v>11916666.66666666</v>
+        <v>11664000</v>
       </c>
       <c r="N28" t="n">
-        <v>79.14393939393939</v>
+        <v>79.00000000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>23.06161369686215</v>
+        <v>23.14342195458392</v>
       </c>
       <c r="P28" t="n">
-        <v>182.2996733080584</v>
+        <v>182.3085980685746</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.584457933370977</v>
+        <v>1.597039333805161</v>
       </c>
       <c r="R28" t="n">
-        <v>77.4817092845043</v>
+        <v>77.56414795711771</v>
       </c>
       <c r="S28" t="n">
-        <v>27706889.09111075</v>
+        <v>27738496.98608804</v>
       </c>
       <c r="T28" t="n">
-        <v>83.52708014035655</v>
+        <v>83.48672153563776</v>
       </c>
       <c r="U28" t="n">
-        <v>24.19146825396825</v>
+        <v>23.86049137336094</v>
       </c>
       <c r="V28" t="n">
-        <v>183.0720899470899</v>
+        <v>182.7170835058661</v>
       </c>
       <c r="W28" t="n">
-        <v>1.242559523809524</v>
+        <v>1.253840579710145</v>
       </c>
       <c r="X28" t="n">
-        <v>70.49652777777777</v>
+        <v>71.08787370600413</v>
       </c>
       <c r="Y28" t="n">
-        <v>4968282.903439154</v>
+        <v>5865789.216701174</v>
       </c>
       <c r="Z28" t="n">
-        <v>75.63210978835978</v>
+        <v>76.36166666666666</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/germany/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/p6_deployment/data/germany/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:Z32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,22 +623,22 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.93048128342246</v>
+        <v>25.97727272727273</v>
       </c>
       <c r="D3" t="n">
-        <v>185.5828877005348</v>
+        <v>185.6306818181818</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>67.12299465240642</v>
+        <v>67.11363636363636</v>
       </c>
       <c r="G3" t="n">
-        <v>1207620.320855615</v>
+        <v>1198721.590909091</v>
       </c>
       <c r="H3" t="n">
-        <v>69.77540106951871</v>
+        <v>69.70454545454545</v>
       </c>
       <c r="I3" t="n">
         <v>25.88363636363636</v>
@@ -659,22 +659,22 @@
         <v>78.27272727272728</v>
       </c>
       <c r="O3" t="n">
-        <v>24.63643790849673</v>
+        <v>24.62760416666667</v>
       </c>
       <c r="P3" t="n">
-        <v>184.0024509803922</v>
+        <v>184.0234375</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>64.77205882352941</v>
+        <v>64.81336805555554</v>
       </c>
       <c r="S3" t="n">
-        <v>957536.7647058824</v>
+        <v>966861.9791666667</v>
       </c>
       <c r="T3" t="n">
-        <v>68.62254901960785</v>
+        <v>68.68923611111111</v>
       </c>
       <c r="U3" t="n">
         <v>26.10392546583851</v>
@@ -793,7 +793,7 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>24.87941074758151</v>
+        <v>24.87941074758152</v>
       </c>
       <c r="V5" t="n">
         <v>182.0659746643728</v>
@@ -802,7 +802,7 @@
         <v>2.147727117943079</v>
       </c>
       <c r="X5" t="n">
-        <v>77.91587622678512</v>
+        <v>77.91587622678513</v>
       </c>
       <c r="Y5" t="n">
         <v>26298143.27481081</v>
@@ -1059,22 +1059,22 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>25.27979797979798</v>
+        <v>25.32299465240642</v>
       </c>
       <c r="J10" t="n">
-        <v>183.9555555555555</v>
+        <v>183.8994652406417</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>68.37878787878789</v>
+        <v>68.35828877005349</v>
       </c>
       <c r="M10" t="n">
-        <v>1701830.808080808</v>
+        <v>1690708.556149733</v>
       </c>
       <c r="N10" t="n">
-        <v>71.61111111111111</v>
+        <v>71.55080213903743</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -1083,22 +1083,22 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>26.1187684112932</v>
+        <v>26.18457831783986</v>
       </c>
       <c r="V10" t="n">
-        <v>182.0825649387339</v>
+        <v>182.0612779089863</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>67.475009919947</v>
+        <v>67.48334383680663</v>
       </c>
       <c r="Y10" t="n">
-        <v>1445442.174413857</v>
+        <v>1437494.328464345</v>
       </c>
       <c r="Z10" t="n">
-        <v>70.65766567916643</v>
+        <v>70.6244564707514</v>
       </c>
     </row>
     <row r="11">
@@ -1141,7 +1141,7 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
-        <v>24.78276685070163</v>
+        <v>24.78276685070164</v>
       </c>
       <c r="V11" t="n">
         <v>185.307395905222</v>
@@ -1257,22 +1257,22 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>25.89015151515151</v>
+        <v>25.90909090909091</v>
       </c>
       <c r="J13" t="n">
-        <v>186.7159090909091</v>
+        <v>186.6600790513834</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>72.85606060606061</v>
+        <v>72.84584980237155</v>
       </c>
       <c r="M13" t="n">
-        <v>4351988.636363637</v>
+        <v>4341600.790513834</v>
       </c>
       <c r="N13" t="n">
-        <v>75.10606060606061</v>
+        <v>75.09090909090909</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -1281,22 +1281,22 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>27.16863641591902</v>
+        <v>27.13732109100729</v>
       </c>
       <c r="V13" t="n">
-        <v>182.88109615827</v>
+        <v>182.9290665226393</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>69.30280581435473</v>
+        <v>69.29181669517209</v>
       </c>
       <c r="Y13" t="n">
-        <v>1835307.126322751</v>
+        <v>1847953.329882677</v>
       </c>
       <c r="Z13" t="n">
-        <v>71.03622469519208</v>
+        <v>71.04263059981396</v>
       </c>
     </row>
     <row r="14">
@@ -1315,22 +1315,22 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>25.13939393939394</v>
+        <v>25.11688311688312</v>
       </c>
       <c r="J14" t="n">
-        <v>186.0848484848485</v>
+        <v>186.1233766233766</v>
       </c>
       <c r="K14" t="n">
-        <v>1.078787878787879</v>
+        <v>1.077922077922078</v>
       </c>
       <c r="L14" t="n">
-        <v>68.64242424242424</v>
+        <v>68.64935064935064</v>
       </c>
       <c r="M14" t="n">
-        <v>1786969.696969697</v>
+        <v>1789935.064935065</v>
       </c>
       <c r="N14" t="n">
-        <v>72.60606060606059</v>
+        <v>72.63636363636364</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -1339,22 +1339,22 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
-        <v>24.97135380722337</v>
+        <v>24.93359336488218</v>
       </c>
       <c r="V14" t="n">
-        <v>186.3218196457327</v>
+        <v>186.3180210489993</v>
       </c>
       <c r="W14" t="n">
-        <v>1.006073153899241</v>
+        <v>1.006506950606329</v>
       </c>
       <c r="X14" t="n">
-        <v>66.1043823326432</v>
+        <v>66.12969535640343</v>
       </c>
       <c r="Y14" t="n">
-        <v>1264679.232804233</v>
+        <v>1283584.892290249</v>
       </c>
       <c r="Z14" t="n">
-        <v>70.90954106280194</v>
+        <v>70.97450828157351</v>
       </c>
     </row>
     <row r="15">
@@ -1431,22 +1431,22 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>25.80681818181818</v>
+        <v>25.8300395256917</v>
       </c>
       <c r="J16" t="n">
-        <v>184.4621212121212</v>
+        <v>184.4901185770751</v>
       </c>
       <c r="K16" t="n">
-        <v>2.321969696969697</v>
+        <v>2.33201581027668</v>
       </c>
       <c r="L16" t="n">
-        <v>80.24621212121212</v>
+        <v>80.31225296442688</v>
       </c>
       <c r="M16" t="n">
-        <v>29456060.60606061</v>
+        <v>29751383.39920948</v>
       </c>
       <c r="N16" t="n">
-        <v>83.11742424242425</v>
+        <v>83.15415019762845</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -1455,22 +1455,22 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="n">
-        <v>24.83647486772487</v>
+        <v>24.84385783298827</v>
       </c>
       <c r="V16" t="n">
-        <v>183.855076058201</v>
+        <v>183.8487750172533</v>
       </c>
       <c r="W16" t="n">
-        <v>1.949900793650794</v>
+        <v>1.962215320910973</v>
       </c>
       <c r="X16" t="n">
-        <v>77.17939814814815</v>
+        <v>77.3852657004831</v>
       </c>
       <c r="Y16" t="n">
-        <v>18144204.6957672</v>
+        <v>18611827.12215321</v>
       </c>
       <c r="Z16" t="n">
-        <v>82.01909722222221</v>
+        <v>82.16485507246377</v>
       </c>
     </row>
     <row r="17">
@@ -1586,7 +1586,7 @@
         <v>4006952.868060768</v>
       </c>
       <c r="Z18" t="n">
-        <v>76.3987690673691</v>
+        <v>76.39876906736912</v>
       </c>
     </row>
     <row r="19">
@@ -1675,22 +1675,22 @@
         <v>70.56363636363636</v>
       </c>
       <c r="I20" t="n">
-        <v>24.26306818181818</v>
+        <v>24.13515151515151</v>
       </c>
       <c r="J20" t="n">
-        <v>184.7460227272728</v>
+        <v>184.7472727272728</v>
       </c>
       <c r="K20" t="n">
-        <v>1.073863636363636</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="L20" t="n">
-        <v>70.53920454545454</v>
+        <v>70.52060606060606</v>
       </c>
       <c r="M20" t="n">
-        <v>2805454.545454545</v>
+        <v>2836121.212121212</v>
       </c>
       <c r="N20" t="n">
-        <v>75.48295454545455</v>
+        <v>75.59393939393939</v>
       </c>
       <c r="O20" t="n">
         <v>24.73087761674718</v>
@@ -1711,22 +1711,22 @@
         <v>70.55429031515989</v>
       </c>
       <c r="U20" t="n">
-        <v>25.91930914242127</v>
+        <v>25.90440594239221</v>
       </c>
       <c r="V20" t="n">
-        <v>183.1085707929244</v>
+        <v>183.115808845786</v>
       </c>
       <c r="W20" t="n">
-        <v>1.209991974955505</v>
+        <v>1.214467630428729</v>
       </c>
       <c r="X20" t="n">
-        <v>68.57220723911227</v>
+        <v>68.62940200743405</v>
       </c>
       <c r="Y20" t="n">
-        <v>1682609.16387436</v>
+        <v>1668354.536704079</v>
       </c>
       <c r="Z20" t="n">
-        <v>73.19443422868767</v>
+        <v>73.29311079631447</v>
       </c>
     </row>
     <row r="21">
@@ -1900,7 +1900,7 @@
         <v>2715412.533068783</v>
       </c>
       <c r="Z23" t="n">
-        <v>74.37838955026456</v>
+        <v>74.37838955026454</v>
       </c>
     </row>
     <row r="24">
@@ -1952,7 +1952,7 @@
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>68.58049072890024</v>
+        <v>68.58049072890026</v>
       </c>
       <c r="Y24" t="n">
         <v>1616511.003404985</v>
@@ -1977,22 +1977,22 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>27.00606060606061</v>
+        <v>26.92857142857143</v>
       </c>
       <c r="J25" t="n">
-        <v>183.7333333333333</v>
+        <v>183.7207792207792</v>
       </c>
       <c r="K25" t="n">
-        <v>1.012121212121212</v>
+        <v>1.012987012987013</v>
       </c>
       <c r="L25" t="n">
-        <v>68.92121212121212</v>
+        <v>68.8896103896104</v>
       </c>
       <c r="M25" t="n">
-        <v>1640000</v>
+        <v>1643506.493506493</v>
       </c>
       <c r="N25" t="n">
-        <v>72.76363636363635</v>
+        <v>72.82467532467531</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -2001,22 +2001,22 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="n">
-        <v>26.53968253968254</v>
+        <v>26.57823129251701</v>
       </c>
       <c r="V25" t="n">
-        <v>183.0027777777777</v>
+        <v>182.9632936507936</v>
       </c>
       <c r="W25" t="n">
-        <v>1.119047619047619</v>
+        <v>1.127551020408163</v>
       </c>
       <c r="X25" t="n">
-        <v>66.70291005291006</v>
+        <v>66.68168934240363</v>
       </c>
       <c r="Y25" t="n">
-        <v>1142956.349206349</v>
+        <v>1140865.929705215</v>
       </c>
       <c r="Z25" t="n">
-        <v>71.3739417989418</v>
+        <v>71.36096938775509</v>
       </c>
     </row>
     <row r="26">
@@ -2138,82 +2138,338 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>26.06363636363636</v>
+      </c>
+      <c r="J28" t="n">
+        <v>183.7435606060606</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.147348484848485</v>
+      </c>
+      <c r="L28" t="n">
+        <v>73.18333333333334</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4895804.924242425</v>
+      </c>
+      <c r="N28" t="n">
+        <v>76.06325757575758</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="n">
+        <v>25.19132267943409</v>
+      </c>
+      <c r="V28" t="n">
+        <v>184.7709140188939</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.259079632202487</v>
+      </c>
+      <c r="X28" t="n">
+        <v>69.18188095540785</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2794284.061792464</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>74.31118405918177</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>25.62857142857143</v>
+      </c>
+      <c r="J29" t="n">
+        <v>181.3642857142857</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>68.15000000000001</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1409642.857142857</v>
+      </c>
+      <c r="N29" t="n">
+        <v>70.42857142857143</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="n">
+        <v>23.17202380952381</v>
+      </c>
+      <c r="V29" t="n">
+        <v>181.225</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>65.63670634920635</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1277291.666666667</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>70.6875</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>25.55189393939394</v>
+      </c>
+      <c r="J30" t="n">
+        <v>186.2450757575758</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.571212121212121</v>
+      </c>
+      <c r="L30" t="n">
+        <v>75.99659090909091</v>
+      </c>
+      <c r="M30" t="n">
+        <v>11083863.63636363</v>
+      </c>
+      <c r="N30" t="n">
+        <v>79.62916666666666</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="n">
+        <v>24.28577898550725</v>
+      </c>
+      <c r="V30" t="n">
+        <v>184.1685185185185</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.25829307568438</v>
+      </c>
+      <c r="X30" t="n">
+        <v>73.47984601449275</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>8048716.787439614</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>78.17277576489532</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>25.69090909090909</v>
+      </c>
+      <c r="D31" t="n">
+        <v>184.7757575757575</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.078787878787879</v>
+      </c>
+      <c r="F31" t="n">
+        <v>67.53333333333333</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1416060.606060606</v>
+      </c>
+      <c r="H31" t="n">
+        <v>71.06666666666666</v>
+      </c>
+      <c r="I31" t="n">
+        <v>24.2054292929293</v>
+      </c>
+      <c r="J31" t="n">
+        <v>183.2920454545455</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.674200336700337</v>
+      </c>
+      <c r="L31" t="n">
+        <v>76.81498316498316</v>
+      </c>
+      <c r="M31" t="n">
+        <v>15183578.49326599</v>
+      </c>
+      <c r="N31" t="n">
+        <v>81.11140572390572</v>
+      </c>
+      <c r="O31" t="n">
+        <v>26.2462962962963</v>
+      </c>
+      <c r="P31" t="n">
+        <v>183.4342592592592</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>66.59722222222223</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1237689.814814815</v>
+      </c>
+      <c r="T31" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="U31" t="n">
+        <v>24.90495228527349</v>
+      </c>
+      <c r="V31" t="n">
+        <v>183.5869284349837</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.499156685534395</v>
+      </c>
+      <c r="X31" t="n">
+        <v>72.18333902939166</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>6228215.411430388</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>78.08648685085412</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="n">
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
         <v>25.53430602319492</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D32" t="n">
         <v>184.4677141788253</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E32" t="n">
         <v>2.169322858211747</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F32" t="n">
         <v>81.66719042274597</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G32" t="n">
         <v>37101945.37972316</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H32" t="n">
         <v>84.42667414889638</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I32" t="n">
         <v>24.39272727272727</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J32" t="n">
         <v>184.7272727272727</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K32" t="n">
         <v>1.534545454545454</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L32" t="n">
         <v>76.11272727272728</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M32" t="n">
         <v>11664000</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N32" t="n">
         <v>79.00000000000001</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O32" t="n">
         <v>23.14342195458392</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P32" t="n">
         <v>182.3085980685746</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q32" t="n">
         <v>1.597039333805161</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R32" t="n">
         <v>77.56414795711771</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S32" t="n">
         <v>27738496.98608804</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T32" t="n">
         <v>83.48672153563776</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U32" t="n">
         <v>23.86049137336094</v>
       </c>
-      <c r="V28" t="n">
+      <c r="V32" t="n">
         <v>182.7170835058661</v>
       </c>
-      <c r="W28" t="n">
+      <c r="W32" t="n">
         <v>1.253840579710145</v>
       </c>
-      <c r="X28" t="n">
+      <c r="X32" t="n">
         <v>71.08787370600413</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Y32" t="n">
         <v>5865789.216701174</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="Z32" t="n">
         <v>76.36166666666666</v>
       </c>
     </row>

--- a/p6_deployment/data/germany/data_preparation/fill_data/df_copiado_formaciones.xlsx
+++ b/p6_deployment/data/germany/data_preparation/fill_data/df_copiado_formaciones.xlsx
@@ -571,22 +571,22 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>25.84363636363636</v>
+        <v>25.85584415584416</v>
       </c>
       <c r="J2" t="n">
-        <v>184.6181818181818</v>
+        <v>185.0896103896104</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>70.08363636363637</v>
+        <v>69.98311688311688</v>
       </c>
       <c r="M2" t="n">
-        <v>2310060.606060606</v>
+        <v>2280129.87012987</v>
       </c>
       <c r="N2" t="n">
-        <v>73.09454545454545</v>
+        <v>72.9948051948052</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -595,22 +595,22 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>26.32033834586466</v>
+        <v>25.9109291084855</v>
       </c>
       <c r="V2" t="n">
-        <v>186.0177443609022</v>
+        <v>185.9665950590763</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>66.88057644110276</v>
+        <v>66.73899033297529</v>
       </c>
       <c r="Y2" t="n">
-        <v>1260743.73433584</v>
+        <v>1282843.716433942</v>
       </c>
       <c r="Z2" t="n">
-        <v>70.93689223057645</v>
+        <v>71.16578947368421</v>
       </c>
     </row>
     <row r="3">
@@ -623,76 +623,76 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>25.97727272727273</v>
+        <v>26.1010101010101</v>
       </c>
       <c r="D3" t="n">
-        <v>185.6306818181818</v>
+        <v>185.7878787878788</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>67.11363636363636</v>
+        <v>67.20202020202019</v>
       </c>
       <c r="G3" t="n">
-        <v>1198721.590909091</v>
+        <v>1204545.454545454</v>
       </c>
       <c r="H3" t="n">
-        <v>69.70454545454545</v>
+        <v>69.61616161616161</v>
       </c>
       <c r="I3" t="n">
-        <v>25.88363636363636</v>
+        <v>25.59848484848484</v>
       </c>
       <c r="J3" t="n">
-        <v>183.4181818181818</v>
+        <v>182.9924242424242</v>
       </c>
       <c r="K3" t="n">
-        <v>1.592727272727272</v>
+        <v>1.568181818181818</v>
       </c>
       <c r="L3" t="n">
-        <v>74.4290909090909</v>
+        <v>74.40151515151514</v>
       </c>
       <c r="M3" t="n">
-        <v>6750181.818181817</v>
+        <v>6821969.696969698</v>
       </c>
       <c r="N3" t="n">
-        <v>78.27272727272728</v>
+        <v>78.58333333333333</v>
       </c>
       <c r="O3" t="n">
-        <v>24.62760416666667</v>
+        <v>24.32561728395062</v>
       </c>
       <c r="P3" t="n">
-        <v>184.0234375</v>
+        <v>183.5354938271605</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>64.81336805555554</v>
+        <v>64.92746913580247</v>
       </c>
       <c r="S3" t="n">
-        <v>966861.9791666667</v>
+        <v>1005285.49382716</v>
       </c>
       <c r="T3" t="n">
-        <v>68.68923611111111</v>
+        <v>69.12654320987654</v>
       </c>
       <c r="U3" t="n">
-        <v>26.10392546583851</v>
+        <v>26.39302248677249</v>
       </c>
       <c r="V3" t="n">
-        <v>184.7884375431332</v>
+        <v>185.5456349206349</v>
       </c>
       <c r="W3" t="n">
-        <v>1.496536231884058</v>
+        <v>1.517526455026455</v>
       </c>
       <c r="X3" t="n">
-        <v>72.19923188405797</v>
+        <v>72.56084656084656</v>
       </c>
       <c r="Y3" t="n">
-        <v>4507439.320220841</v>
+        <v>4633196.924603174</v>
       </c>
       <c r="Z3" t="n">
-        <v>76.34969082125603</v>
+        <v>76.51157407407408</v>
       </c>
     </row>
     <row r="4">
@@ -711,22 +711,22 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>26.43181818181818</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="J4" t="n">
-        <v>185.7916666666667</v>
+        <v>185.6363636363637</v>
       </c>
       <c r="K4" t="n">
-        <v>1.78030303030303</v>
+        <v>1.818181818181818</v>
       </c>
       <c r="L4" t="n">
-        <v>75.21590909090908</v>
+        <v>75.33333333333334</v>
       </c>
       <c r="M4" t="n">
-        <v>8631818.181818182</v>
+        <v>8990909.090909092</v>
       </c>
       <c r="N4" t="n">
-        <v>78.88257575757576</v>
+        <v>78.75757575757575</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -735,22 +735,22 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>24.32393389118932</v>
+        <v>24.380291005291</v>
       </c>
       <c r="V4" t="n">
-        <v>184.7463804060272</v>
+        <v>185.2876984126984</v>
       </c>
       <c r="W4" t="n">
-        <v>1.346938262019783</v>
+        <v>1.371858465608465</v>
       </c>
       <c r="X4" t="n">
-        <v>70.98909449045318</v>
+        <v>71.54580026455027</v>
       </c>
       <c r="Y4" t="n">
-        <v>4994844.414970095</v>
+        <v>5163723.544973545</v>
       </c>
       <c r="Z4" t="n">
-        <v>77.42874036691971</v>
+        <v>77.71660052910052</v>
       </c>
     </row>
     <row r="5">
@@ -769,22 +769,22 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>27.18560606060606</v>
+        <v>27.17424242424243</v>
       </c>
       <c r="J5" t="n">
-        <v>185.1931818181818</v>
+        <v>184.9469696969697</v>
       </c>
       <c r="K5" t="n">
-        <v>3.143939393939394</v>
+        <v>3.015151515151516</v>
       </c>
       <c r="L5" t="n">
-        <v>82.46969696969698</v>
+        <v>81.68939393939394</v>
       </c>
       <c r="M5" t="n">
-        <v>45745265.15151515</v>
+        <v>39014393.93939394</v>
       </c>
       <c r="N5" t="n">
-        <v>84.97727272727273</v>
+        <v>84.40151515151514</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -793,22 +793,22 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>24.87941074758152</v>
+        <v>24.45712106352839</v>
       </c>
       <c r="V5" t="n">
-        <v>182.0659746643728</v>
+        <v>182.0672128347328</v>
       </c>
       <c r="W5" t="n">
-        <v>2.147727117943079</v>
+        <v>2.167504152343969</v>
       </c>
       <c r="X5" t="n">
-        <v>77.91587622678513</v>
+        <v>77.9537588584714</v>
       </c>
       <c r="Y5" t="n">
-        <v>26298143.27481081</v>
+        <v>27552763.46238964</v>
       </c>
       <c r="Z5" t="n">
-        <v>83.04825326725356</v>
+        <v>83.28191797978697</v>
       </c>
     </row>
     <row r="6">
@@ -827,22 +827,22 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>24.84925252525252</v>
+        <v>25.36186868686869</v>
       </c>
       <c r="J6" t="n">
-        <v>184.8076767676768</v>
+        <v>184.8122895622895</v>
       </c>
       <c r="K6" t="n">
-        <v>1.49220202020202</v>
+        <v>1.506902356902357</v>
       </c>
       <c r="L6" t="n">
-        <v>75.25357575757576</v>
+        <v>75.14865319865319</v>
       </c>
       <c r="M6" t="n">
-        <v>8616650.505050505</v>
+        <v>8163392.255892255</v>
       </c>
       <c r="N6" t="n">
-        <v>78.27482828282828</v>
+        <v>78.04478114478115</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -851,22 +851,22 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>23.43553056554429</v>
+        <v>22.77183947186808</v>
       </c>
       <c r="V6" t="n">
-        <v>183.4115297482838</v>
+        <v>183.8194072136864</v>
       </c>
       <c r="W6" t="n">
-        <v>1.295255403000254</v>
+        <v>1.2656941266209</v>
       </c>
       <c r="X6" t="n">
-        <v>72.71196026297628</v>
+        <v>72.58214274363445</v>
       </c>
       <c r="Y6" t="n">
-        <v>6241387.857324472</v>
+        <v>6659763.062547673</v>
       </c>
       <c r="Z6" t="n">
-        <v>78.22619705059751</v>
+        <v>78.87316184482945</v>
       </c>
     </row>
     <row r="7">
@@ -885,22 +885,22 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>23.73030303030303</v>
+        <v>23.81558441558441</v>
       </c>
       <c r="J7" t="n">
-        <v>183.2090909090909</v>
+        <v>183.0974025974026</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>69.14181818181818</v>
+        <v>68.95974025974024</v>
       </c>
       <c r="M7" t="n">
-        <v>2332030.303030303</v>
+        <v>2284870.12987013</v>
       </c>
       <c r="N7" t="n">
-        <v>75.36121212121212</v>
+        <v>75.07402597402597</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -909,22 +909,22 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>22.88650793650794</v>
+        <v>22.53741496598639</v>
       </c>
       <c r="V7" t="n">
-        <v>183.4554232804233</v>
+        <v>183.7338435374149</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>63.91600529100528</v>
+        <v>63.16808390022675</v>
       </c>
       <c r="Y7" t="n">
-        <v>1211101.190476191</v>
+        <v>1147456.065759637</v>
       </c>
       <c r="Z7" t="n">
-        <v>71.86428571428571</v>
+        <v>72.031179138322</v>
       </c>
     </row>
     <row r="8">
@@ -943,22 +943,22 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>26.28</v>
+        <v>25.81428571428571</v>
       </c>
       <c r="J8" t="n">
-        <v>185.8266666666667</v>
+        <v>186.4857142857143</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>69.52666666666667</v>
+        <v>68.95714285714287</v>
       </c>
       <c r="M8" t="n">
-        <v>1836666.666666667</v>
+        <v>1752500</v>
       </c>
       <c r="N8" t="n">
-        <v>73.32666666666667</v>
+        <v>73.78571428571429</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -967,22 +967,22 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>25.59672364672365</v>
+        <v>24.8501221001221</v>
       </c>
       <c r="V8" t="n">
-        <v>185.5155270655271</v>
+        <v>184.8923992673993</v>
       </c>
       <c r="W8" t="n">
-        <v>1.075925925925926</v>
+        <v>1.033730158730159</v>
       </c>
       <c r="X8" t="n">
-        <v>67.41816239316239</v>
+        <v>66.65201465201464</v>
       </c>
       <c r="Y8" t="n">
-        <v>1430449.786324786</v>
+        <v>1401608.669108669</v>
       </c>
       <c r="Z8" t="n">
-        <v>72.78931623931622</v>
+        <v>72.44337606837607</v>
       </c>
     </row>
     <row r="9">
@@ -1001,22 +1001,22 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>27.01090909090909</v>
+        <v>26.92424242424242</v>
       </c>
       <c r="J9" t="n">
-        <v>184.9454545454546</v>
+        <v>184.7045454545455</v>
       </c>
       <c r="K9" t="n">
-        <v>1.629090909090909</v>
+        <v>1.606060606060606</v>
       </c>
       <c r="L9" t="n">
-        <v>75.80727272727273</v>
+        <v>75.81060606060606</v>
       </c>
       <c r="M9" t="n">
-        <v>8416181.818181818</v>
+        <v>8463636.363636365</v>
       </c>
       <c r="N9" t="n">
-        <v>78.08000000000001</v>
+        <v>78.24242424242425</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -1025,22 +1025,22 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>26.84057934691802</v>
+        <v>26.95259586163476</v>
       </c>
       <c r="V9" t="n">
-        <v>183.9944046710981</v>
+        <v>184.4976023240469</v>
       </c>
       <c r="W9" t="n">
-        <v>1.480745523228361</v>
+        <v>1.469145765985011</v>
       </c>
       <c r="X9" t="n">
-        <v>73.74021230612765</v>
+        <v>73.88470156369185</v>
       </c>
       <c r="Y9" t="n">
-        <v>5214261.759471141</v>
+        <v>5168253.665564879</v>
       </c>
       <c r="Z9" t="n">
-        <v>76.13055464748828</v>
+        <v>76.10069255263764</v>
       </c>
     </row>
     <row r="10">
@@ -1059,22 +1059,22 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>25.32299465240642</v>
+        <v>25.39886363636364</v>
       </c>
       <c r="J10" t="n">
-        <v>183.8994652406417</v>
+        <v>183.7329545454546</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>68.35828877005349</v>
+        <v>68.33522727272728</v>
       </c>
       <c r="M10" t="n">
-        <v>1690708.556149733</v>
+        <v>1673380.681818182</v>
       </c>
       <c r="N10" t="n">
-        <v>71.55080213903743</v>
+        <v>71.47499999999999</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -1083,22 +1083,22 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>26.18457831783986</v>
+        <v>26.49465948096526</v>
       </c>
       <c r="V10" t="n">
-        <v>182.0612779089863</v>
+        <v>181.2934100010402</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>67.48334383680663</v>
+        <v>67.60523065321406</v>
       </c>
       <c r="Y10" t="n">
-        <v>1437494.328464345</v>
+        <v>1398703.22576451</v>
       </c>
       <c r="Z10" t="n">
-        <v>70.6244564707514</v>
+        <v>70.25405333368005</v>
       </c>
     </row>
     <row r="11">
@@ -1117,22 +1117,22 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>25.01515151515152</v>
+        <v>24.65909090909091</v>
       </c>
       <c r="J11" t="n">
-        <v>182.7034090909091</v>
+        <v>182.8272727272727</v>
       </c>
       <c r="K11" t="n">
-        <v>2.114772727272727</v>
+        <v>2.075757575757576</v>
       </c>
       <c r="L11" t="n">
-        <v>80.2594696969697</v>
+        <v>80.28181818181818</v>
       </c>
       <c r="M11" t="n">
-        <v>28676704.54545455</v>
+        <v>29237121.21212121</v>
       </c>
       <c r="N11" t="n">
-        <v>83.63409090909092</v>
+        <v>83.88939393939394</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -1141,22 +1141,22 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
-        <v>24.78276685070164</v>
+        <v>24.99997843340235</v>
       </c>
       <c r="V11" t="n">
-        <v>185.307395905222</v>
+        <v>184.8588106740281</v>
       </c>
       <c r="W11" t="n">
-        <v>1.666533672647803</v>
+        <v>1.721043248217162</v>
       </c>
       <c r="X11" t="n">
-        <v>76.70394453071084</v>
+        <v>76.84006211180125</v>
       </c>
       <c r="Y11" t="n">
-        <v>17697117.9836669</v>
+        <v>17745793.79457097</v>
       </c>
       <c r="Z11" t="n">
-        <v>81.43627070393374</v>
+        <v>81.4256599378882</v>
       </c>
     </row>
     <row r="12">
@@ -1169,76 +1169,76 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>25.55090909090909</v>
+        <v>25.6987012987013</v>
       </c>
       <c r="D12" t="n">
-        <v>183.4945454545455</v>
+        <v>183.5805194805195</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>67.17090909090909</v>
+        <v>66.98181818181818</v>
       </c>
       <c r="G12" t="n">
-        <v>1433590.909090909</v>
+        <v>1359707.792207792</v>
       </c>
       <c r="H12" t="n">
-        <v>71.06242424242424</v>
+        <v>70.96493506493506</v>
       </c>
       <c r="I12" t="n">
-        <v>27.23484848484849</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="J12" t="n">
-        <v>183.7840909090909</v>
+        <v>183.5681818181818</v>
       </c>
       <c r="K12" t="n">
-        <v>1.712121212121212</v>
+        <v>1.696969696969697</v>
       </c>
       <c r="L12" t="n">
-        <v>75.54924242424242</v>
+        <v>75.43939393939394</v>
       </c>
       <c r="M12" t="n">
-        <v>9118181.818181818</v>
+        <v>8703787.878787877</v>
       </c>
       <c r="N12" t="n">
-        <v>77.40151515151516</v>
+        <v>77.17424242424242</v>
       </c>
       <c r="O12" t="n">
-        <v>26.20886243386243</v>
+        <v>25.67375283446712</v>
       </c>
       <c r="P12" t="n">
-        <v>185.1949735449735</v>
+        <v>184.3086734693877</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>66.5681216931217</v>
+        <v>66.60827664399093</v>
       </c>
       <c r="S12" t="n">
-        <v>1171283.068783069</v>
+        <v>1250368.480725624</v>
       </c>
       <c r="T12" t="n">
-        <v>69.75132275132275</v>
+        <v>69.77069160997732</v>
       </c>
       <c r="U12" t="n">
-        <v>24.99484444807672</v>
+        <v>24.72535573535288</v>
       </c>
       <c r="V12" t="n">
-        <v>184.9159408560653</v>
+        <v>184.9018840125676</v>
       </c>
       <c r="W12" t="n">
-        <v>1.470589479435303</v>
+        <v>1.432053412516799</v>
       </c>
       <c r="X12" t="n">
-        <v>73.55038975003936</v>
+        <v>73.17647538229632</v>
       </c>
       <c r="Y12" t="n">
-        <v>6272273.95367949</v>
+        <v>5758952.669263739</v>
       </c>
       <c r="Z12" t="n">
-        <v>76.75503260339859</v>
+        <v>76.68100924866513</v>
       </c>
     </row>
     <row r="13">
@@ -1257,22 +1257,22 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>25.90909090909091</v>
+        <v>25.64393939393939</v>
       </c>
       <c r="J13" t="n">
-        <v>186.6600790513834</v>
+        <v>186.6818181818182</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>72.84584980237155</v>
+        <v>72.91666666666667</v>
       </c>
       <c r="M13" t="n">
-        <v>4341600.790513834</v>
+        <v>4475189.393939394</v>
       </c>
       <c r="N13" t="n">
-        <v>75.09090909090909</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -1281,22 +1281,22 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>27.13732109100729</v>
+        <v>27.22056878306878</v>
       </c>
       <c r="V13" t="n">
-        <v>182.9290665226393</v>
+        <v>183.088458994709</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>69.29181669517209</v>
+        <v>69.15658068783068</v>
       </c>
       <c r="Y13" t="n">
-        <v>1847953.329882677</v>
+        <v>1897767.857142857</v>
       </c>
       <c r="Z13" t="n">
-        <v>71.04263059981396</v>
+        <v>70.8599537037037</v>
       </c>
     </row>
     <row r="14">
@@ -1315,22 +1315,22 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>25.11688311688312</v>
+        <v>25.24675324675325</v>
       </c>
       <c r="J14" t="n">
-        <v>186.1233766233766</v>
+        <v>186.4545454545454</v>
       </c>
       <c r="K14" t="n">
         <v>1.077922077922078</v>
       </c>
       <c r="L14" t="n">
-        <v>68.64935064935064</v>
+        <v>68.55844155844156</v>
       </c>
       <c r="M14" t="n">
-        <v>1789935.064935065</v>
+        <v>1760389.610389611</v>
       </c>
       <c r="N14" t="n">
-        <v>72.63636363636364</v>
+        <v>72.53246753246754</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -1339,22 +1339,22 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
-        <v>24.93359336488218</v>
+        <v>25.11718672976437</v>
       </c>
       <c r="V14" t="n">
-        <v>186.3180210489993</v>
+        <v>186.0427881297447</v>
       </c>
       <c r="W14" t="n">
-        <v>1.006506950606329</v>
+        <v>1.013013901212659</v>
       </c>
       <c r="X14" t="n">
-        <v>66.12969535640343</v>
+        <v>66.52923198264814</v>
       </c>
       <c r="Y14" t="n">
-        <v>1283584.892290249</v>
+        <v>1377735.260770975</v>
       </c>
       <c r="Z14" t="n">
-        <v>70.97450828157351</v>
+        <v>71.19108005521049</v>
       </c>
     </row>
     <row r="15">
@@ -1373,22 +1373,22 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>25.90909090909091</v>
+        <v>25.72727272727272</v>
       </c>
       <c r="J15" t="n">
-        <v>183.6121212121212</v>
+        <v>183.6233766233766</v>
       </c>
       <c r="K15" t="n">
-        <v>1.16969696969697</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="L15" t="n">
-        <v>69.7818181818182</v>
+        <v>69.63636363636364</v>
       </c>
       <c r="M15" t="n">
-        <v>2006363.636363636</v>
+        <v>2008441.558441559</v>
       </c>
       <c r="N15" t="n">
-        <v>73.73333333333333</v>
+        <v>73.83116883116882</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -1397,22 +1397,22 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>24.07195767195767</v>
+        <v>24.08078231292517</v>
       </c>
       <c r="V15" t="n">
-        <v>184.3002645502646</v>
+        <v>183.9410430839002</v>
       </c>
       <c r="W15" t="n">
         <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>66.04722222222222</v>
+        <v>66.1686507936508</v>
       </c>
       <c r="Y15" t="n">
-        <v>1300539.021164021</v>
+        <v>1337414.965986395</v>
       </c>
       <c r="Z15" t="n">
-        <v>71.710582010582</v>
+        <v>71.44727891156462</v>
       </c>
     </row>
     <row r="16">
@@ -1431,22 +1431,22 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>25.8300395256917</v>
+        <v>25.3030303030303</v>
       </c>
       <c r="J16" t="n">
-        <v>184.4901185770751</v>
+        <v>184.6363636363636</v>
       </c>
       <c r="K16" t="n">
-        <v>2.33201581027668</v>
+        <v>2.295454545454545</v>
       </c>
       <c r="L16" t="n">
-        <v>80.31225296442688</v>
+        <v>79.88636363636364</v>
       </c>
       <c r="M16" t="n">
-        <v>29751383.39920948</v>
+        <v>29481060.60606061</v>
       </c>
       <c r="N16" t="n">
-        <v>83.15415019762845</v>
+        <v>83.25757575757576</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -1455,22 +1455,22 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="n">
-        <v>24.84385783298827</v>
+        <v>25.150958994709</v>
       </c>
       <c r="V16" t="n">
-        <v>183.8487750172533</v>
+        <v>183.9763558201058</v>
       </c>
       <c r="W16" t="n">
-        <v>1.962215320910973</v>
+        <v>2.013227513227513</v>
       </c>
       <c r="X16" t="n">
-        <v>77.3852657004831</v>
+        <v>77.81018518518518</v>
       </c>
       <c r="Y16" t="n">
-        <v>18611827.12215321</v>
+        <v>20326719.57671958</v>
       </c>
       <c r="Z16" t="n">
-        <v>82.16485507246377</v>
+        <v>82.11458333333333</v>
       </c>
     </row>
     <row r="17">
@@ -1489,22 +1489,22 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>23.75151515151515</v>
+        <v>23.4025974025974</v>
       </c>
       <c r="J17" t="n">
-        <v>183.9030303030303</v>
+        <v>183.3506493506493</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>67.47272727272727</v>
+        <v>67.16883116883118</v>
       </c>
       <c r="M17" t="n">
-        <v>1659090.909090909</v>
+        <v>1636688.311688312</v>
       </c>
       <c r="N17" t="n">
-        <v>73.03636363636363</v>
+        <v>73.16883116883116</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -1513,22 +1513,22 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="n">
-        <v>26.40824915824916</v>
+        <v>27.22204184704185</v>
       </c>
       <c r="V17" t="n">
-        <v>183.167760942761</v>
+        <v>182.7880591630591</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>66.72912457912459</v>
+        <v>67.27272727272728</v>
       </c>
       <c r="Y17" t="n">
-        <v>1104993.686868687</v>
+        <v>1142446.789321789</v>
       </c>
       <c r="Z17" t="n">
-        <v>69.79309764309764</v>
+        <v>69.34433621933621</v>
       </c>
     </row>
     <row r="18">
@@ -1547,22 +1547,22 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>25.65046296296296</v>
+        <v>25.36296296296297</v>
       </c>
       <c r="J18" t="n">
-        <v>185.8619107744108</v>
+        <v>185.9469696969697</v>
       </c>
       <c r="K18" t="n">
-        <v>1.45976430976431</v>
+        <v>1.440824915824916</v>
       </c>
       <c r="L18" t="n">
-        <v>74.625</v>
+        <v>74.36851851851851</v>
       </c>
       <c r="M18" t="n">
-        <v>6710662.878787879</v>
+        <v>6684659.090909091</v>
       </c>
       <c r="N18" t="n">
-        <v>77.19234006734007</v>
+        <v>77.4013468013468</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -1571,22 +1571,22 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="n">
-        <v>24.30819129718607</v>
+        <v>23.83559237424369</v>
       </c>
       <c r="V18" t="n">
-        <v>183.6187468960205</v>
+        <v>184.5199887344624</v>
       </c>
       <c r="W18" t="n">
-        <v>1.147585874129024</v>
+        <v>1.132095785549733</v>
       </c>
       <c r="X18" t="n">
-        <v>71.62761588453829</v>
+        <v>70.95658440609098</v>
       </c>
       <c r="Y18" t="n">
-        <v>4006952.868060768</v>
+        <v>3835458.293381813</v>
       </c>
       <c r="Z18" t="n">
-        <v>76.39876906736912</v>
+        <v>76.48222109883294</v>
       </c>
     </row>
     <row r="19">
@@ -1605,22 +1605,22 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>24.03515151515152</v>
+        <v>23.94545454545455</v>
       </c>
       <c r="J19" t="n">
-        <v>185.7927272727273</v>
+        <v>185.6987012987013</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>66.72363636363637</v>
+        <v>66.48571428571429</v>
       </c>
       <c r="M19" t="n">
-        <v>1459409.090909091</v>
+        <v>1437370.12987013</v>
       </c>
       <c r="N19" t="n">
-        <v>72.31393939393939</v>
+        <v>72.51688311688312</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -1629,22 +1629,22 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="n">
-        <v>24.71506263462785</v>
+        <v>25.11362628055175</v>
       </c>
       <c r="V19" t="n">
-        <v>185.7294984001506</v>
+        <v>186.4101496329757</v>
       </c>
       <c r="W19" t="n">
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>66.6373611895351</v>
+        <v>67.01883520206501</v>
       </c>
       <c r="Y19" t="n">
-        <v>1347724.371039589</v>
+        <v>1372780.96515286</v>
       </c>
       <c r="Z19" t="n">
-        <v>71.76849342284125</v>
+        <v>71.23804146164395</v>
       </c>
     </row>
     <row r="20">
@@ -1657,76 +1657,76 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>26.54969696969697</v>
+        <v>26.55844155844155</v>
       </c>
       <c r="D20" t="n">
-        <v>184.3387878787879</v>
+        <v>183.7662337662337</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>67.76242424242425</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="G20" t="n">
-        <v>1327106.060606061</v>
+        <v>1327922.077922078</v>
       </c>
       <c r="H20" t="n">
-        <v>70.56363636363636</v>
+        <v>70.49350649350649</v>
       </c>
       <c r="I20" t="n">
-        <v>24.13515151515151</v>
+        <v>24.14285714285714</v>
       </c>
       <c r="J20" t="n">
-        <v>184.7472727272728</v>
+        <v>184.6714285714286</v>
       </c>
       <c r="K20" t="n">
-        <v>1.066666666666667</v>
+        <v>1.071428571428572</v>
       </c>
       <c r="L20" t="n">
-        <v>70.52060606060606</v>
+        <v>70.58571428571429</v>
       </c>
       <c r="M20" t="n">
-        <v>2836121.212121212</v>
+        <v>2848571.428571429</v>
       </c>
       <c r="N20" t="n">
-        <v>75.59393939393939</v>
+        <v>75.45714285714287</v>
       </c>
       <c r="O20" t="n">
-        <v>24.73087761674718</v>
+        <v>25.16707335107956</v>
       </c>
       <c r="P20" t="n">
-        <v>183.3894007361399</v>
+        <v>183.6615276545401</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>66.39468599033816</v>
+        <v>66.62325002464753</v>
       </c>
       <c r="S20" t="n">
-        <v>1208483.868184955</v>
+        <v>1202547.631371389</v>
       </c>
       <c r="T20" t="n">
-        <v>70.55429031515989</v>
+        <v>70.29122301094351</v>
       </c>
       <c r="U20" t="n">
-        <v>25.90440594239221</v>
+        <v>25.75887441170213</v>
       </c>
       <c r="V20" t="n">
-        <v>183.115808845786</v>
+        <v>183.161994011945</v>
       </c>
       <c r="W20" t="n">
-        <v>1.214467630428729</v>
+        <v>1.230265103753172</v>
       </c>
       <c r="X20" t="n">
-        <v>68.62940200743405</v>
+        <v>68.67751677329971</v>
       </c>
       <c r="Y20" t="n">
-        <v>1668354.536704079</v>
+        <v>1714543.735114183</v>
       </c>
       <c r="Z20" t="n">
-        <v>73.29311079631447</v>
+        <v>73.62469320298676</v>
       </c>
     </row>
     <row r="21">
@@ -1745,22 +1745,22 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>25.08484848484848</v>
+        <v>25.2987012987013</v>
       </c>
       <c r="J21" t="n">
-        <v>182.4909090909091</v>
+        <v>182.1038961038961</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>67.2909090909091</v>
+        <v>67.24675324675324</v>
       </c>
       <c r="M21" t="n">
-        <v>1338393.93939394</v>
+        <v>1323831.168831169</v>
       </c>
       <c r="N21" t="n">
-        <v>70.96969696969697</v>
+        <v>70.93506493506494</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -1769,22 +1769,22 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
-        <v>27.9031746031746</v>
+        <v>27.87244897959183</v>
       </c>
       <c r="V21" t="n">
-        <v>181.1016471734893</v>
+        <v>180.7478607232367</v>
       </c>
       <c r="W21" t="n">
         <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>64.24054859370649</v>
+        <v>64.68581274615109</v>
       </c>
       <c r="Y21" t="n">
-        <v>731285.8047897521</v>
+        <v>767403.8220551378</v>
       </c>
       <c r="Z21" t="n">
-        <v>65.70394458368143</v>
+        <v>66.2298245614035</v>
       </c>
     </row>
     <row r="22">
@@ -1803,22 +1803,22 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>27.92777777777778</v>
+        <v>27.8968253968254</v>
       </c>
       <c r="J22" t="n">
-        <v>183.1965811965812</v>
+        <v>182.5682539682539</v>
       </c>
       <c r="K22" t="n">
-        <v>1.265811965811966</v>
+        <v>1.253174603174603</v>
       </c>
       <c r="L22" t="n">
-        <v>73.1794871794872</v>
+        <v>73.20793650793651</v>
       </c>
       <c r="M22" t="n">
-        <v>3630032.051282051</v>
+        <v>3635853.174603175</v>
       </c>
       <c r="N22" t="n">
-        <v>75.15897435897435</v>
+        <v>75.08888888888889</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
@@ -1827,22 +1827,22 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="n">
-        <v>26.73745421245421</v>
+        <v>26.92941930395347</v>
       </c>
       <c r="V22" t="n">
-        <v>182.4158289460349</v>
+        <v>182.6555353304209</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04545714900406</v>
+        <v>1.075362448564475</v>
       </c>
       <c r="X22" t="n">
-        <v>70.09494745973578</v>
+        <v>70.67002245874427</v>
       </c>
       <c r="Y22" t="n">
-        <v>2184121.574697233</v>
+        <v>2429647.014204059</v>
       </c>
       <c r="Z22" t="n">
-        <v>73.0017850665734</v>
+        <v>73.44407969033257</v>
       </c>
     </row>
     <row r="23">
@@ -1861,22 +1861,22 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>24.37878787878788</v>
+        <v>24.46969696969697</v>
       </c>
       <c r="J23" t="n">
-        <v>185.1439393939394</v>
+        <v>184.9924242424242</v>
       </c>
       <c r="K23" t="n">
-        <v>1.295454545454546</v>
+        <v>1.340909090909091</v>
       </c>
       <c r="L23" t="n">
-        <v>72.5719696969697</v>
+        <v>72.67424242424242</v>
       </c>
       <c r="M23" t="n">
-        <v>5912878.787878788</v>
+        <v>6025757.575757575</v>
       </c>
       <c r="N23" t="n">
-        <v>77.85606060606061</v>
+        <v>77.86363636363636</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -1885,22 +1885,22 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="n">
-        <v>25.79629629629629</v>
+        <v>25.85069444444445</v>
       </c>
       <c r="V23" t="n">
-        <v>185.338210978836</v>
+        <v>184.9386574074074</v>
       </c>
       <c r="W23" t="n">
-        <v>1.261739417989418</v>
+        <v>1.31712962962963</v>
       </c>
       <c r="X23" t="n">
-        <v>69.37003968253968</v>
+        <v>69.62847222222223</v>
       </c>
       <c r="Y23" t="n">
-        <v>2715412.533068783</v>
+        <v>2937488.425925925</v>
       </c>
       <c r="Z23" t="n">
-        <v>74.37838955026454</v>
+        <v>74.60995370370371</v>
       </c>
     </row>
     <row r="24">
@@ -1919,22 +1919,22 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>26.21919191919192</v>
+        <v>25.8030303030303</v>
       </c>
       <c r="J24" t="n">
-        <v>185.9505892255892</v>
+        <v>186.569696969697</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>70.73985690235691</v>
+        <v>70.64848484848484</v>
       </c>
       <c r="M24" t="n">
-        <v>2382124.368686868</v>
+        <v>2422405.303030303</v>
       </c>
       <c r="N24" t="n">
-        <v>73.69482323232323</v>
+        <v>74.09242424242423</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
@@ -1943,22 +1943,22 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="n">
-        <v>26.09022927407678</v>
+        <v>26.23151387366541</v>
       </c>
       <c r="V24" t="n">
-        <v>187.1591262652404</v>
+        <v>186.5838739360479</v>
       </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>68.58049072890026</v>
+        <v>68.65077326824449</v>
       </c>
       <c r="Y24" t="n">
-        <v>1616511.003404985</v>
+        <v>1616994.789763732</v>
       </c>
       <c r="Z24" t="n">
-        <v>71.57790316005629</v>
+        <v>71.31078389085103</v>
       </c>
     </row>
     <row r="25">
@@ -1977,22 +1977,22 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>26.92857142857143</v>
+        <v>26.66233766233767</v>
       </c>
       <c r="J25" t="n">
-        <v>183.7207792207792</v>
+        <v>183.4935064935065</v>
       </c>
       <c r="K25" t="n">
-        <v>1.012987012987013</v>
+        <v>1.025974025974026</v>
       </c>
       <c r="L25" t="n">
-        <v>68.8896103896104</v>
+        <v>68.6883116883117</v>
       </c>
       <c r="M25" t="n">
-        <v>1643506.493506493</v>
+        <v>1667532.467532468</v>
       </c>
       <c r="N25" t="n">
-        <v>72.82467532467531</v>
+        <v>72.98701298701299</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -2001,22 +2001,22 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="n">
-        <v>26.57823129251701</v>
+        <v>27.28344671201814</v>
       </c>
       <c r="V25" t="n">
-        <v>182.9632936507936</v>
+        <v>182.563492063492</v>
       </c>
       <c r="W25" t="n">
-        <v>1.127551020408163</v>
+        <v>1.219387755102041</v>
       </c>
       <c r="X25" t="n">
-        <v>66.68168934240363</v>
+        <v>67.30187074829932</v>
       </c>
       <c r="Y25" t="n">
-        <v>1140865.929705215</v>
+        <v>1239321.145124716</v>
       </c>
       <c r="Z25" t="n">
-        <v>71.36096938775509</v>
+        <v>71.34495464852607</v>
       </c>
     </row>
     <row r="26">
@@ -2035,22 +2035,22 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>24.6569696969697</v>
+        <v>24.61558441558442</v>
       </c>
       <c r="J26" t="n">
-        <v>183.4224242424243</v>
+        <v>183.074025974026</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>70.77696969696969</v>
+        <v>70.61298701298701</v>
       </c>
       <c r="M26" t="n">
-        <v>2776363.636363636</v>
+        <v>2690909.090909091</v>
       </c>
       <c r="N26" t="n">
-        <v>74.53636363636363</v>
+        <v>74.3831168831169</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
@@ -2059,22 +2059,22 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="n">
-        <v>25.16001683501684</v>
+        <v>25.27146464646465</v>
       </c>
       <c r="V26" t="n">
-        <v>181.9852212602213</v>
+        <v>181.5678210678211</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>69.51005291005292</v>
+        <v>70.17460317460318</v>
       </c>
       <c r="Y26" t="n">
-        <v>2252022.607022607</v>
+        <v>2475252.525252525</v>
       </c>
       <c r="Z26" t="n">
-        <v>73.00972823472824</v>
+        <v>73.31421356421356</v>
       </c>
     </row>
     <row r="27">
@@ -2093,22 +2093,22 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>25.11111111111111</v>
+        <v>25.31313131313131</v>
       </c>
       <c r="J27" t="n">
-        <v>184.4848484848485</v>
+        <v>184.6868686868687</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>70.1919191919192</v>
+        <v>70.50505050505051</v>
       </c>
       <c r="M27" t="n">
-        <v>2569696.96969697</v>
+        <v>2639646.464646464</v>
       </c>
       <c r="N27" t="n">
-        <v>74.17676767676767</v>
+        <v>74.05050505050505</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -2117,22 +2117,22 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="n">
-        <v>23.50694444444444</v>
+        <v>24.04938271604938</v>
       </c>
       <c r="V27" t="n">
-        <v>186.0601851851852</v>
+        <v>185.7808641975309</v>
       </c>
       <c r="W27" t="n">
         <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>66.11882716049382</v>
+        <v>67.11111111111111</v>
       </c>
       <c r="Y27" t="n">
-        <v>1558275.462962963</v>
+        <v>1687337.962962963</v>
       </c>
       <c r="Z27" t="n">
-        <v>72.07793209876543</v>
+        <v>72.63117283950618</v>
       </c>
     </row>
     <row r="28">
@@ -2151,22 +2151,22 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>26.06363636363636</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="J28" t="n">
-        <v>183.7435606060606</v>
+        <v>183.030303030303</v>
       </c>
       <c r="K28" t="n">
-        <v>1.147348484848485</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="L28" t="n">
-        <v>73.18333333333334</v>
+        <v>73.31818181818181</v>
       </c>
       <c r="M28" t="n">
-        <v>4895804.924242425</v>
+        <v>4940530.303030304</v>
       </c>
       <c r="N28" t="n">
-        <v>76.06325757575758</v>
+        <v>76.03030303030303</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
@@ -2175,22 +2175,22 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="n">
-        <v>25.19132267943409</v>
+        <v>24.85555052334944</v>
       </c>
       <c r="V28" t="n">
-        <v>184.7709140188939</v>
+        <v>184.9186611985882</v>
       </c>
       <c r="W28" t="n">
-        <v>1.259079632202487</v>
+        <v>1.13635859727822</v>
       </c>
       <c r="X28" t="n">
-        <v>69.18188095540785</v>
+        <v>68.48530406632523</v>
       </c>
       <c r="Y28" t="n">
-        <v>2794284.061792464</v>
+        <v>2511872.270122771</v>
       </c>
       <c r="Z28" t="n">
-        <v>74.31118405918177</v>
+        <v>73.9932057650164</v>
       </c>
     </row>
     <row r="29">
@@ -2209,22 +2209,22 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>25.62857142857143</v>
+        <v>25.52857142857143</v>
       </c>
       <c r="J29" t="n">
-        <v>181.3642857142857</v>
+        <v>181.3142857142857</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>68.15000000000001</v>
+        <v>68.24285714285713</v>
       </c>
       <c r="M29" t="n">
-        <v>1409642.857142857</v>
+        <v>1449285.714285714</v>
       </c>
       <c r="N29" t="n">
-        <v>70.42857142857143</v>
+        <v>70.65714285714286</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
@@ -2233,22 +2233,22 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="n">
-        <v>23.17202380952381</v>
+        <v>22.80436507936508</v>
       </c>
       <c r="V29" t="n">
-        <v>181.225</v>
+        <v>180.4956349206349</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>65.63670634920635</v>
+        <v>65.29126984126984</v>
       </c>
       <c r="Y29" t="n">
-        <v>1277291.666666667</v>
+        <v>1244017.857142857</v>
       </c>
       <c r="Z29" t="n">
-        <v>70.6875</v>
+        <v>70.66071428571429</v>
       </c>
     </row>
     <row r="30">
@@ -2267,22 +2267,22 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>25.55189393939394</v>
+        <v>25.31666666666667</v>
       </c>
       <c r="J30" t="n">
-        <v>186.2450757575758</v>
+        <v>186.7</v>
       </c>
       <c r="K30" t="n">
-        <v>1.571212121212121</v>
+        <v>1.566666666666666</v>
       </c>
       <c r="L30" t="n">
-        <v>75.99659090909091</v>
+        <v>75.875</v>
       </c>
       <c r="M30" t="n">
-        <v>11083863.63636363</v>
+        <v>10947500</v>
       </c>
       <c r="N30" t="n">
-        <v>79.62916666666666</v>
+        <v>79.58333333333333</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
@@ -2291,22 +2291,22 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="n">
-        <v>24.28577898550725</v>
+        <v>24.36808574879227</v>
       </c>
       <c r="V30" t="n">
-        <v>184.1685185185185</v>
+        <v>183.4844907407407</v>
       </c>
       <c r="W30" t="n">
-        <v>1.25829307568438</v>
+        <v>1.255012077294686</v>
       </c>
       <c r="X30" t="n">
-        <v>73.47984601449275</v>
+        <v>73.56385869565217</v>
       </c>
       <c r="Y30" t="n">
-        <v>8048716.787439614</v>
+        <v>8261773.852657005</v>
       </c>
       <c r="Z30" t="n">
-        <v>78.17277576489532</v>
+        <v>78.34231078904992</v>
       </c>
     </row>
     <row r="31">
@@ -2319,76 +2319,76 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>25.69090909090909</v>
+        <v>25.48051948051948</v>
       </c>
       <c r="D31" t="n">
-        <v>184.7757575757575</v>
+        <v>184.5584415584416</v>
       </c>
       <c r="E31" t="n">
-        <v>1.078787878787879</v>
+        <v>1.064935064935065</v>
       </c>
       <c r="F31" t="n">
-        <v>67.53333333333333</v>
+        <v>67.40259740259741</v>
       </c>
       <c r="G31" t="n">
-        <v>1416060.606060606</v>
+        <v>1417207.792207792</v>
       </c>
       <c r="H31" t="n">
-        <v>71.06666666666666</v>
+        <v>71.09090909090909</v>
       </c>
       <c r="I31" t="n">
-        <v>24.2054292929293</v>
+        <v>24.17314814814815</v>
       </c>
       <c r="J31" t="n">
-        <v>183.2920454545455</v>
+        <v>183.1722222222222</v>
       </c>
       <c r="K31" t="n">
-        <v>1.674200336700337</v>
+        <v>1.65462962962963</v>
       </c>
       <c r="L31" t="n">
-        <v>76.81498316498316</v>
+        <v>76.78055555555555</v>
       </c>
       <c r="M31" t="n">
-        <v>15183578.49326599</v>
+        <v>15412175.92592593</v>
       </c>
       <c r="N31" t="n">
-        <v>81.11140572390572</v>
+        <v>81.16944444444444</v>
       </c>
       <c r="O31" t="n">
-        <v>26.2462962962963</v>
+        <v>26.19444444444444</v>
       </c>
       <c r="P31" t="n">
-        <v>183.4342592592592</v>
+        <v>182.3432539682539</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>66.59722222222223</v>
+        <v>66.7876984126984</v>
       </c>
       <c r="S31" t="n">
-        <v>1237689.814814815</v>
+        <v>1275128.968253969</v>
       </c>
       <c r="T31" t="n">
-        <v>69.95</v>
+        <v>70.03571428571429</v>
       </c>
       <c r="U31" t="n">
-        <v>24.90495228527349</v>
+        <v>24.15238522442469</v>
       </c>
       <c r="V31" t="n">
-        <v>183.5869284349837</v>
+        <v>183.9373034859877</v>
       </c>
       <c r="W31" t="n">
-        <v>1.499156685534395</v>
+        <v>1.403607028935976</v>
       </c>
       <c r="X31" t="n">
-        <v>72.18333902939166</v>
+        <v>71.64384256094782</v>
       </c>
       <c r="Y31" t="n">
-        <v>6228215.411430388</v>
+        <v>5468893.576270222</v>
       </c>
       <c r="Z31" t="n">
-        <v>78.08648685085412</v>
+        <v>78.40204346092503</v>
       </c>
     </row>
     <row r="32">
@@ -2401,76 +2401,76 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>25.53430602319492</v>
+        <v>25.62494172494172</v>
       </c>
       <c r="D32" t="n">
-        <v>184.4677141788253</v>
+        <v>185.2397047397047</v>
       </c>
       <c r="E32" t="n">
-        <v>2.169322858211747</v>
+        <v>2.02937062937063</v>
       </c>
       <c r="F32" t="n">
-        <v>81.66719042274597</v>
+        <v>81.18275058275057</v>
       </c>
       <c r="G32" t="n">
-        <v>37101945.37972316</v>
+        <v>32260644.91064491</v>
       </c>
       <c r="H32" t="n">
-        <v>84.42667414889638</v>
+        <v>84.09184149184148</v>
       </c>
       <c r="I32" t="n">
-        <v>24.39272727272727</v>
+        <v>24.37121212121212</v>
       </c>
       <c r="J32" t="n">
-        <v>184.7272727272727</v>
+        <v>184.6439393939394</v>
       </c>
       <c r="K32" t="n">
-        <v>1.534545454545454</v>
+        <v>1.5</v>
       </c>
       <c r="L32" t="n">
-        <v>76.11272727272728</v>
+        <v>76.06060606060606</v>
       </c>
       <c r="M32" t="n">
-        <v>11664000</v>
+        <v>11783333.33333333</v>
       </c>
       <c r="N32" t="n">
-        <v>79.00000000000001</v>
+        <v>79.18181818181817</v>
       </c>
       <c r="O32" t="n">
-        <v>23.14342195458392</v>
+        <v>22.9557055263577</v>
       </c>
       <c r="P32" t="n">
-        <v>182.3085980685746</v>
+        <v>181.5306546714155</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.597039333805161</v>
+        <v>1.768393924915664</v>
       </c>
       <c r="R32" t="n">
-        <v>77.56414795711771</v>
+        <v>79.01045548654244</v>
       </c>
       <c r="S32" t="n">
-        <v>27738496.98608804</v>
+        <v>35925979.835382</v>
       </c>
       <c r="T32" t="n">
-        <v>83.48672153563776</v>
+        <v>84.46879443020747</v>
       </c>
       <c r="U32" t="n">
-        <v>23.86049137336094</v>
+        <v>24.37645502645502</v>
       </c>
       <c r="V32" t="n">
-        <v>182.7170835058661</v>
+        <v>182.4883597883598</v>
       </c>
       <c r="W32" t="n">
-        <v>1.253840579710145</v>
+        <v>1.278604497354497</v>
       </c>
       <c r="X32" t="n">
-        <v>71.08787370600413</v>
+        <v>71.13700396825396</v>
       </c>
       <c r="Y32" t="n">
-        <v>5865789.216701174</v>
+        <v>5657118.882275132</v>
       </c>
       <c r="Z32" t="n">
-        <v>76.36166666666666</v>
+        <v>75.64880952380953</v>
       </c>
     </row>
   </sheetData>
